--- a/data/outputSpecialityRpt/File1/RPT_RPT2772174638977HO_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT2772174638977HO_outputSpecialityRpt.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$1526.4923043018746</t>
+          <t>$1526.4923043018744</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$1853.1489524912922</t>
+          <t>$1853.1489524912927</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$8141.301187683422</t>
+          <t>$8141.30118768342</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$9883.471882140664</t>
+          <t>$9883.471882140666</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$2035.321960143317</t>
+          <t>$2035.3219601433166</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$2470.8639197150064</t>
+          <t>$2470.863919715007</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$333306.75895494246</t>
+          <t>$333306.7589549424</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$457481.1164482863</t>
+          <t>$457481.1164482864</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$461501.6662453049</t>
+          <t>$461501.6662453048</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$633435.3920053195</t>
+          <t>$633435.3920053196</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$358945.74041301495</t>
+          <t>$358945.74041301484</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$492671.9715596929</t>
+          <t>$492671.971559693</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$76077.06803166986</t>
+          <t>$76077.06803166984</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$91437.51129216883</t>
+          <t>$91437.51129216884</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$6016.685677920803</t>
+          <t>$6016.685677920802</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$7531.934263994481</t>
+          <t>$7531.934263994482</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$-2.3120942268951787e-11</t>
+          <t>$-2.3120942268951793e-11</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$104180.40717602456</t>
+          <t>$104180.40717602454</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$128483.41299951497</t>
+          <t>$128483.412999515</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$493881.35462339164</t>
+          <t>$493881.3546233915</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$609093.0509766757</t>
+          <t>$609093.0509766758</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$15013.218839338528</t>
+          <t>$15013.218839338524</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$7411.817829474306</t>
+          <t>$7411.8178294743075</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$2866.2677323939147</t>
+          <t>$2866.267732393914</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$3134.3353233545545</t>
+          <t>$3134.3353233545554</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$15943.534788831297</t>
+          <t>$15943.534788831294</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$19823.04196539372</t>
+          <t>$19823.041965393724</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$1081182.0246411501</t>
+          <t>$1081182.02464115</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$2090856.9081313584</t>
+          <t>$2090856.908131359</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="P31" s="14" t="inlineStr">
         <is>
-          <t>$2445011.0921800314</t>
+          <t>$2445011.092180031</t>
         </is>
       </c>
       <c r="Q31" s="14" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="S31" s="14" t="inlineStr">
         <is>
-          <t>$4778711.577924198</t>
+          <t>$4778711.5779241985</t>
         </is>
       </c>
       <c r="T31" s="14" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="P32" s="14" t="inlineStr">
         <is>
-          <t>$60102.078622383626</t>
+          <t>$60102.07862238361</t>
         </is>
       </c>
       <c r="Q32" s="14" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="S32" s="14" t="inlineStr">
         <is>
-          <t>$122918.39504539444</t>
+          <t>$122918.39504539447</t>
         </is>
       </c>
       <c r="T32" s="14" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P33" s="14" t="inlineStr">
         <is>
-          <t>$7971.767394415649</t>
+          <t>$7971.767394415647</t>
         </is>
       </c>
       <c r="Q33" s="14" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="S33" s="14" t="inlineStr">
         <is>
-          <t>$9911.52098269686</t>
+          <t>$9911.520982696862</t>
         </is>
       </c>
       <c r="T33" s="14" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P34" s="14" t="inlineStr">
         <is>
-          <t>$70261.84036532322</t>
+          <t>$70261.84036532321</t>
         </is>
       </c>
       <c r="Q34" s="14" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="S34" s="14" t="inlineStr">
         <is>
-          <t>$94048.8554980129</t>
+          <t>$94048.85549801293</t>
         </is>
       </c>
       <c r="T34" s="14" t="inlineStr">
@@ -3689,7 +3689,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N35" s="14" t="n">
         <v>1.401051026134051</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S35" s="14" t="inlineStr">
         <is>
-          <t>$22290.941037274053</t>
+          <t>$22290.94103727405</t>
         </is>
       </c>
       <c r="T35" s="14" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="P36" s="14" t="inlineStr">
         <is>
-          <t>$341842.8207139507</t>
+          <t>$341842.82071395067</t>
         </is>
       </c>
       <c r="Q36" s="14" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="S36" s="14" t="inlineStr">
         <is>
-          <t>$195025.76751221326</t>
+          <t>$195025.76751221332</t>
         </is>
       </c>
       <c r="T36" s="14" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="P39" s="14" t="inlineStr">
         <is>
-          <t>$195587.41436355986</t>
+          <t>$195587.41436355983</t>
         </is>
       </c>
       <c r="Q39" s="14" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="S39" s="14" t="inlineStr">
         <is>
-          <t>$267156.29580852453</t>
+          <t>$267156.2958085246</t>
         </is>
       </c>
       <c r="T39" s="14" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="P40" s="14" t="inlineStr">
         <is>
-          <t>$11805.736494154042</t>
+          <t>$11805.736494154038</t>
         </is>
       </c>
       <c r="Q40" s="14" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="S40" s="14" t="inlineStr">
         <is>
-          <t>$15802.546585931628</t>
+          <t>$15802.546585931632</t>
         </is>
       </c>
       <c r="T40" s="14" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P42" s="14" t="inlineStr">
         <is>
-          <t>$7509.580802393848</t>
+          <t>$7509.580802393846</t>
         </is>
       </c>
       <c r="Q42" s="14" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="S42" s="14" t="inlineStr">
         <is>
-          <t>$9331.336231352445</t>
+          <t>$9331.336231352447</t>
         </is>
       </c>
       <c r="T42" s="14" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="P44" s="14" t="inlineStr">
         <is>
-          <t>$100152.5773823762</t>
+          <t>$100152.57738237617</t>
         </is>
       </c>
       <c r="Q44" s="14" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="S44" s="14" t="inlineStr">
         <is>
-          <t>$58133.13194439136</t>
+          <t>$58133.131944391374</t>
         </is>
       </c>
       <c r="T44" s="14" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P46" s="14" t="inlineStr">
         <is>
-          <t>$27075.715183167227</t>
+          <t>$27075.71518316722</t>
         </is>
       </c>
       <c r="Q46" s="14" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="S46" s="14" t="inlineStr">
         <is>
-          <t>$24822.345964043074</t>
+          <t>$24822.345964043077</t>
         </is>
       </c>
       <c r="T46" s="14" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="P47" s="14" t="inlineStr">
         <is>
-          <t>$4032800.4146745875</t>
+          <t>$4032800.4146745866</t>
         </is>
       </c>
       <c r="Q47" s="14" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="S47" s="14" t="inlineStr">
         <is>
-          <t>$2803867.508608767</t>
+          <t>$2803867.5086087678</t>
         </is>
       </c>
       <c r="T47" s="14" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="P48" s="14" t="inlineStr">
         <is>
-          <t>$20820.605380635883</t>
+          <t>$20820.60538063588</t>
         </is>
       </c>
       <c r="Q48" s="14" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="S48" s="14" t="inlineStr">
         <is>
-          <t>$21923.10955698286</t>
+          <t>$21923.109556982865</t>
         </is>
       </c>
       <c r="T48" s="14" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="P49" s="14" t="inlineStr">
         <is>
-          <t>$45995.2869953062</t>
+          <t>$45995.286995306196</t>
         </is>
       </c>
       <c r="Q49" s="14" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="S49" s="14" t="inlineStr">
         <is>
-          <t>$46523.56017922692</t>
+          <t>$46523.56017922693</t>
         </is>
       </c>
       <c r="T49" s="14" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="P50" s="14" t="inlineStr">
         <is>
-          <t>$7665.84732672655</t>
+          <t>$7665.847326726549</t>
         </is>
       </c>
       <c r="Q50" s="14" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="S50" s="14" t="inlineStr">
         <is>
-          <t>$7753.892468724536</t>
+          <t>$7753.892468724538</t>
         </is>
       </c>
       <c r="T50" s="14" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="P51" s="14" t="inlineStr">
         <is>
-          <t>$31258.861684960568</t>
+          <t>$31258.86168496056</t>
         </is>
       </c>
       <c r="Q51" s="14" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="S51" s="14" t="inlineStr">
         <is>
-          <t>$56451.63300170151</t>
+          <t>$56451.63300170153</t>
         </is>
       </c>
       <c r="T51" s="14" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P52" s="14" t="inlineStr">
         <is>
-          <t>$1433801.2608308892</t>
+          <t>$1433801.2608308888</t>
         </is>
       </c>
       <c r="Q52" s="14" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="S52" s="14" t="inlineStr">
         <is>
-          <t>$1457934.37772194</t>
+          <t>$1457934.3777219402</t>
         </is>
       </c>
       <c r="T52" s="14" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P53" s="14" t="inlineStr">
         <is>
-          <t>$686.2063459763993</t>
+          <t>$686.2063459763992</t>
         </is>
       </c>
       <c r="Q53" s="14" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="S53" s="14" t="inlineStr">
         <is>
-          <t>$927.0151873735855</t>
+          <t>$927.0151873735857</t>
         </is>
       </c>
       <c r="T53" s="14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="P54" s="14" t="inlineStr">
         <is>
-          <t>$8036.320972616988</t>
+          <t>$8036.320972616986</t>
         </is>
       </c>
       <c r="Q54" s="14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="S54" s="14" t="inlineStr">
         <is>
-          <t>$10855.979849806004</t>
+          <t>$10855.979849806006</t>
         </is>
       </c>
       <c r="T54" s="14" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="P55" s="14" t="inlineStr">
         <is>
-          <t>$23526.706028427492</t>
+          <t>$23526.706028427485</t>
         </is>
       </c>
       <c r="Q55" s="14" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="S55" s="14" t="inlineStr">
         <is>
-          <t>$31783.701555677715</t>
+          <t>$31783.701555677722</t>
         </is>
       </c>
       <c r="T55" s="14" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="P56" s="14" t="inlineStr">
         <is>
-          <t>$197908.51504395323</t>
+          <t>$197908.5150439532</t>
         </is>
       </c>
       <c r="Q56" s="14" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="S56" s="14" t="inlineStr">
         <is>
-          <t>$248999.1263671326</t>
+          <t>$248999.12636713265</t>
         </is>
       </c>
       <c r="T56" s="14" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="P57" s="14" t="inlineStr">
         <is>
-          <t>$5077.847524400879</t>
+          <t>$5077.847524400877</t>
         </is>
       </c>
       <c r="Q57" s="14" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="S57" s="14" t="inlineStr">
         <is>
-          <t>$6859.982441476607</t>
+          <t>$6859.982441476608</t>
         </is>
       </c>
       <c r="T57" s="14" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="P58" s="14" t="inlineStr">
         <is>
-          <t>$1928.4978687448718</t>
+          <t>$1928.4978687448713</t>
         </is>
       </c>
       <c r="Q58" s="14" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="S58" s="14" t="inlineStr">
         <is>
-          <t>$2030.6167512411948</t>
+          <t>$2030.6167512411953</t>
         </is>
       </c>
       <c r="T58" s="14" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="P59" s="14" t="inlineStr">
         <is>
-          <t>$132.9448224105902</t>
+          <t>$132.94482241059018</t>
         </is>
       </c>
       <c r="Q59" s="14" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="S59" s="14" t="inlineStr">
         <is>
-          <t>$139.98458995105293</t>
+          <t>$139.98458995105295</t>
         </is>
       </c>
       <c r="T59" s="14" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="P60" s="14" t="inlineStr">
         <is>
-          <t>$152777.18475618027</t>
+          <t>$152777.18475618024</t>
         </is>
       </c>
       <c r="Q60" s="14" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="S60" s="14" t="inlineStr">
         <is>
-          <t>$312073.9642892403</t>
+          <t>$312073.96428924036</t>
         </is>
       </c>
       <c r="T60" s="14" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="P61" s="14" t="inlineStr">
         <is>
-          <t>$509257.2825918105</t>
+          <t>$509257.28259181045</t>
         </is>
       </c>
       <c r="Q61" s="14" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="S61" s="14" t="inlineStr">
         <is>
-          <t>$1040246.547776259</t>
+          <t>$1040246.5477762592</t>
         </is>
       </c>
       <c r="T61" s="14" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P62" s="14" t="inlineStr">
         <is>
-          <t>$458331.5541403636</t>
+          <t>$458331.55414036347</t>
         </is>
       </c>
       <c r="Q62" s="14" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="S62" s="14" t="inlineStr">
         <is>
-          <t>$936221.8926058965</t>
+          <t>$936221.8926058967</t>
         </is>
       </c>
       <c r="T62" s="14" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P63" s="14" t="inlineStr">
         <is>
-          <t>$16217.094399223184</t>
+          <t>$16217.09439922318</t>
         </is>
       </c>
       <c r="Q63" s="14" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="S63" s="14" t="inlineStr">
         <is>
-          <t>$16440.072511372164</t>
+          <t>$16440.072511372167</t>
         </is>
       </c>
       <c r="T63" s="14" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="P64" s="14" t="inlineStr">
         <is>
-          <t>$2037806.2676705734</t>
+          <t>$2037806.267670573</t>
         </is>
       </c>
       <c r="Q64" s="14" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="S64" s="14" t="inlineStr">
         <is>
-          <t>$3584263.7094392194</t>
+          <t>$3584263.7094392204</t>
         </is>
       </c>
       <c r="T64" s="14" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="P65" s="14" t="inlineStr">
         <is>
-          <t>$621625.0504994751</t>
+          <t>$621625.050499475</t>
         </is>
       </c>
       <c r="Q65" s="14" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="S65" s="14" t="inlineStr">
         <is>
-          <t>$1215056.4819250763</t>
+          <t>$1215056.4819250766</t>
         </is>
       </c>
       <c r="T65" s="14" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="P66" s="14" t="inlineStr">
         <is>
-          <t>$109951.08724238692</t>
+          <t>$109951.08724238689</t>
         </is>
       </c>
       <c r="Q66" s="14" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="S66" s="14" t="inlineStr">
         <is>
-          <t>$214369.14666251643</t>
+          <t>$214369.14666251646</t>
         </is>
       </c>
       <c r="T66" s="14" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P67" s="14" t="inlineStr">
         <is>
-          <t>$91990.1679207186</t>
+          <t>$91990.16792071857</t>
         </is>
       </c>
       <c r="Q67" s="14" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="S67" s="14" t="inlineStr">
         <is>
-          <t>$93046.70962469444</t>
+          <t>$93046.70962469446</t>
         </is>
       </c>
       <c r="T67" s="14" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P68" s="14" t="inlineStr">
         <is>
-          <t>$145926.73191143465</t>
+          <t>$145926.73191143462</t>
         </is>
       </c>
       <c r="Q68" s="14" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="S68" s="14" t="inlineStr">
         <is>
-          <t>$148241.58802017407</t>
+          <t>$148241.5880201741</t>
         </is>
       </c>
       <c r="T68" s="14" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P69" s="14" t="inlineStr">
         <is>
-          <t>$139685.26296047185</t>
+          <t>$139685.26296047182</t>
         </is>
       </c>
       <c r="Q69" s="14" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="S69" s="14" t="inlineStr">
         <is>
-          <t>$285331.4376386034</t>
+          <t>$285331.43763860344</t>
         </is>
       </c>
       <c r="T69" s="14" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="P70" s="14" t="inlineStr">
         <is>
-          <t>$259795.51949011983</t>
+          <t>$259795.51949011977</t>
         </is>
       </c>
       <c r="Q70" s="14" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="S70" s="14" t="inlineStr">
         <is>
-          <t>$304371.7815413176</t>
+          <t>$304371.78154131764</t>
         </is>
       </c>
       <c r="T70" s="14" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P71" s="14" t="inlineStr">
         <is>
-          <t>$181831.41445712833</t>
+          <t>$181831.4144571283</t>
         </is>
       </c>
       <c r="Q71" s="14" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="S71" s="14" t="inlineStr">
         <is>
-          <t>$212474.7386094253</t>
+          <t>$212474.73860942535</t>
         </is>
       </c>
       <c r="T71" s="14" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="P72" s="14" t="inlineStr">
         <is>
-          <t>$113160.2180443618</t>
+          <t>$113160.21804436177</t>
         </is>
       </c>
       <c r="Q72" s="14" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="S72" s="14" t="inlineStr">
         <is>
-          <t>$146612.16569767217</t>
+          <t>$146612.16569767223</t>
         </is>
       </c>
       <c r="T72" s="14" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="P73" s="14" t="inlineStr">
         <is>
-          <t>$45264.087217744716</t>
+          <t>$45264.0872177447</t>
         </is>
       </c>
       <c r="Q73" s="14" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="S73" s="14" t="inlineStr">
         <is>
-          <t>$58644.86627906887</t>
+          <t>$58644.86627906888</t>
         </is>
       </c>
       <c r="T73" s="14" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="P74" s="14" t="inlineStr">
         <is>
-          <t>$25815.984220538114</t>
+          <t>$25815.984220538106</t>
         </is>
       </c>
       <c r="Q74" s="14" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="S74" s="14" t="inlineStr">
         <is>
-          <t>$31870.974185115025</t>
+          <t>$31870.974185115032</t>
         </is>
       </c>
       <c r="T74" s="14" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="P75" s="14" t="inlineStr">
         <is>
-          <t>$107185.6367272304</t>
+          <t>$107185.63672723039</t>
         </is>
       </c>
       <c r="Q75" s="14" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="S75" s="14" t="inlineStr">
         <is>
-          <t>$162699.8653906081</t>
+          <t>$162699.86539060812</t>
         </is>
       </c>
       <c r="T75" s="14" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P76" s="14" t="inlineStr">
         <is>
-          <t>$257746.54698891548</t>
+          <t>$257746.54698891542</t>
         </is>
       </c>
       <c r="Q76" s="14" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="S76" s="14" t="inlineStr">
         <is>
-          <t>$371631.3109403883</t>
+          <t>$371631.3109403884</t>
         </is>
       </c>
       <c r="T76" s="14" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P77" s="14" t="inlineStr">
         <is>
-          <t>$48508.10135899927</t>
+          <t>$48508.10135899926</t>
         </is>
       </c>
       <c r="Q77" s="14" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="S77" s="14" t="inlineStr">
         <is>
-          <t>$46957.458612812086</t>
+          <t>$46957.4586128121</t>
         </is>
       </c>
       <c r="T77" s="14" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="P78" s="14" t="inlineStr">
         <is>
-          <t>$116634.14553095316</t>
+          <t>$116634.14553095313</t>
         </is>
       </c>
       <c r="Q78" s="14" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="S78" s="14" t="inlineStr">
         <is>
-          <t>$116736.08880931603</t>
+          <t>$116736.08880931605</t>
         </is>
       </c>
       <c r="T78" s="14" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="P79" s="14" t="inlineStr">
         <is>
-          <t>$598062.792149263</t>
+          <t>$598062.7921492629</t>
         </is>
       </c>
       <c r="Q79" s="14" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="S79" s="14" t="inlineStr">
         <is>
-          <t>$679334.4338913905</t>
+          <t>$679334.4338913906</t>
         </is>
       </c>
       <c r="T79" s="14" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="P80" s="14" t="inlineStr">
         <is>
-          <t>$103348.09467521508</t>
+          <t>$103348.09467521506</t>
         </is>
       </c>
       <c r="Q80" s="14" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="S80" s="14" t="inlineStr">
         <is>
-          <t>$151331.86997655095</t>
+          <t>$151331.86997655098</t>
         </is>
       </c>
       <c r="T80" s="14" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="P81" s="14" t="inlineStr">
         <is>
-          <t>$26042.8927896518</t>
+          <t>$26042.892789651793</t>
         </is>
       </c>
       <c r="Q81" s="14" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="S81" s="14" t="inlineStr">
         <is>
-          <t>$13580.387886513696</t>
+          <t>$13580.3878865137</t>
         </is>
       </c>
       <c r="T81" s="14" t="inlineStr">
@@ -10409,7 +10409,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M83" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N83" s="14" t="n">
         <v>1.401051026134051</v>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="S83" s="14" t="inlineStr">
         <is>
-          <t>$14581.771868796357</t>
+          <t>$14581.771868796355</t>
         </is>
       </c>
       <c r="T83" s="14" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="P84" s="14" t="inlineStr">
         <is>
-          <t>$25058.4652492544</t>
+          <t>$25058.465249254394</t>
         </is>
       </c>
       <c r="Q84" s="14" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="S84" s="14" t="inlineStr">
         <is>
-          <t>$32588.76698404332</t>
+          <t>$32588.766984043326</t>
         </is>
       </c>
       <c r="T84" s="14" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P85" s="14" t="inlineStr">
         <is>
-          <t>$200467.7219940352</t>
+          <t>$200467.72199403515</t>
         </is>
       </c>
       <c r="Q85" s="14" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="S85" s="14" t="inlineStr">
         <is>
-          <t>$260710.13587234655</t>
+          <t>$260710.1358723466</t>
         </is>
       </c>
       <c r="T85" s="14" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="P86" s="14" t="inlineStr">
         <is>
-          <t>$333291.1058890235</t>
+          <t>$333291.10588902346</t>
         </is>
       </c>
       <c r="Q86" s="14" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="S86" s="14" t="inlineStr">
         <is>
-          <t>$548470.6802269006</t>
+          <t>$548470.6802269007</t>
         </is>
       </c>
       <c r="T86" s="14" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="P87" s="14" t="inlineStr">
         <is>
-          <t>$12779.114773125966</t>
+          <t>$12779.114773125964</t>
         </is>
       </c>
       <c r="Q87" s="14" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="S87" s="14" t="inlineStr">
         <is>
-          <t>$20284.25215546261</t>
+          <t>$20284.25215546262</t>
         </is>
       </c>
       <c r="T87" s="14" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="P88" s="14" t="inlineStr">
         <is>
-          <t>$690251.9258833718</t>
+          <t>$690251.9258833717</t>
         </is>
       </c>
       <c r="Q88" s="14" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="S88" s="14" t="inlineStr">
         <is>
-          <t>$925474.7105692115</t>
+          <t>$925474.7105692116</t>
         </is>
       </c>
       <c r="T88" s="14" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="P89" s="14" t="inlineStr">
         <is>
-          <t>$398222.46537054505</t>
+          <t>$398222.46537054493</t>
         </is>
       </c>
       <c r="Q89" s="14" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="S89" s="14" t="inlineStr">
         <is>
-          <t>$533927.4764855973</t>
+          <t>$533927.4764855974</t>
         </is>
       </c>
       <c r="T89" s="14" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P90" s="14" t="inlineStr">
         <is>
-          <t>$287443.9416674746</t>
+          <t>$287443.9416674745</t>
         </is>
       </c>
       <c r="Q90" s="14" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="S90" s="14" t="inlineStr">
         <is>
-          <t>$372038.6372097225</t>
+          <t>$372038.63720972254</t>
         </is>
       </c>
       <c r="T90" s="14" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="P91" s="14" t="inlineStr">
         <is>
-          <t>$209050.13939452695</t>
+          <t>$209050.1393945269</t>
         </is>
       </c>
       <c r="Q91" s="14" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="S91" s="14" t="inlineStr">
         <is>
-          <t>$270573.5543343436</t>
+          <t>$270573.55433434364</t>
         </is>
       </c>
       <c r="T91" s="14" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="P92" s="14" t="inlineStr">
         <is>
-          <t>$82857.97282865705</t>
+          <t>$82857.97282865703</t>
         </is>
       </c>
       <c r="Q92" s="14" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="S92" s="14" t="inlineStr">
         <is>
-          <t>$131030.07860909245</t>
+          <t>$131030.07860909248</t>
         </is>
       </c>
       <c r="T92" s="14" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="P93" s="14" t="inlineStr">
         <is>
-          <t>$163032.21323090294</t>
+          <t>$163032.21323090288</t>
         </is>
       </c>
       <c r="Q93" s="14" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="S93" s="14" t="inlineStr">
         <is>
-          <t>$257816.1519789352</t>
+          <t>$257816.15197893526</t>
         </is>
       </c>
       <c r="T93" s="14" t="inlineStr">
@@ -12089,7 +12089,7 @@
         <v>7.77094900292849</v>
       </c>
       <c r="M95" s="14" t="n">
-        <v>7.293955002015849</v>
+        <v>7.293955002015848</v>
       </c>
       <c r="N95" s="14" t="n">
         <v>6.847977842880375</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="S95" s="14" t="inlineStr">
         <is>
-          <t>$45890.355824241036</t>
+          <t>$45890.35582424103</t>
         </is>
       </c>
       <c r="T95" s="14" t="inlineStr">
@@ -12649,7 +12649,7 @@
         <v>5.080650906748497</v>
       </c>
       <c r="M99" s="14" t="n">
-        <v>5.335332950518983</v>
+        <v>5.335332950518982</v>
       </c>
       <c r="N99" s="14" t="n">
         <v>5.604204104536204</v>
@@ -12789,7 +12789,7 @@
         <v>7.620976360122746</v>
       </c>
       <c r="M100" s="14" t="n">
-        <v>8.002999425778475</v>
+        <v>8.002999425778473</v>
       </c>
       <c r="N100" s="14" t="n">
         <v>8.406306156804307</v>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="S100" s="14" t="inlineStr">
         <is>
-          <t>$115294.97079069818</t>
+          <t>$115294.97079069816</t>
         </is>
       </c>
       <c r="T100" s="14" t="inlineStr">
@@ -13461,7 +13461,9 @@
           <t>JASCAYD</t>
         </is>
       </c>
-      <c r="F105" s="14" t="inlineStr"/>
+      <c r="F105" s="14" t="n">
+        <v/>
+      </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
           <t>B</t>
@@ -13497,7 +13499,7 @@
       </c>
       <c r="P105" s="14" t="inlineStr">
         <is>
-          <t>$51730.35764956513</t>
+          <t>$51730.357649565114</t>
         </is>
       </c>
       <c r="Q105" s="14" t="inlineStr">
@@ -13512,7 +13514,7 @@
       </c>
       <c r="S105" s="14" t="inlineStr">
         <is>
-          <t>$82111.4480372857</t>
+          <t>$82111.44803728572</t>
         </is>
       </c>
       <c r="T105" s="14" t="inlineStr">
@@ -13625,7 +13627,7 @@
         <v>7.620976360122746</v>
       </c>
       <c r="M106" s="14" t="n">
-        <v>8.002999425778475</v>
+        <v>8.002999425778473</v>
       </c>
       <c r="N106" s="14" t="n">
         <v>8.406306156804307</v>
@@ -13652,7 +13654,7 @@
       </c>
       <c r="S106" s="14" t="inlineStr">
         <is>
-          <t>$128854.90123255912</t>
+          <t>$128854.9012325591</t>
         </is>
       </c>
       <c r="T106" s="14" t="inlineStr">
@@ -13777,7 +13779,7 @@
       </c>
       <c r="P107" s="14" t="inlineStr">
         <is>
-          <t>$70577.89093912645</t>
+          <t>$70577.89093912643</t>
         </is>
       </c>
       <c r="Q107" s="14" t="inlineStr">
@@ -13792,7 +13794,7 @@
       </c>
       <c r="S107" s="14" t="inlineStr">
         <is>
-          <t>$98107.52409429157</t>
+          <t>$98107.52409429158</t>
         </is>
       </c>
       <c r="T107" s="14" t="inlineStr">
@@ -13917,7 +13919,7 @@
       </c>
       <c r="P108" s="14" t="inlineStr">
         <is>
-          <t>$50660.432701630394</t>
+          <t>$50660.43270163039</t>
         </is>
       </c>
       <c r="Q108" s="14" t="inlineStr">
@@ -13932,7 +13934,7 @@
       </c>
       <c r="S108" s="14" t="inlineStr">
         <is>
-          <t>$80669.1537926159</t>
+          <t>$80669.15379261592</t>
         </is>
       </c>
       <c r="T108" s="14" t="inlineStr">
@@ -14057,7 +14059,7 @@
       </c>
       <c r="P109" s="14" t="inlineStr">
         <is>
-          <t>$211670.02378977137</t>
+          <t>$211670.0237897713</t>
         </is>
       </c>
       <c r="Q109" s="14" t="inlineStr">
@@ -14072,7 +14074,7 @@
       </c>
       <c r="S109" s="14" t="inlineStr">
         <is>
-          <t>$284965.2761357913</t>
+          <t>$284965.2761357914</t>
         </is>
       </c>
       <c r="T109" s="14" t="inlineStr">
@@ -14352,7 +14354,7 @@
       </c>
       <c r="S111" s="14" t="inlineStr">
         <is>
-          <t>$4505.611354117712</t>
+          <t>$4505.611354117711</t>
         </is>
       </c>
       <c r="T111" s="14" t="inlineStr">
@@ -14772,7 +14774,7 @@
       </c>
       <c r="S114" s="14" t="inlineStr">
         <is>
-          <t>$123853.1283652946</t>
+          <t>$123853.12836529459</t>
         </is>
       </c>
       <c r="T114" s="14" t="inlineStr">
@@ -14912,7 +14914,7 @@
       </c>
       <c r="S115" s="14" t="inlineStr">
         <is>
-          <t>$46036.074165513106</t>
+          <t>$46036.0741655131</t>
         </is>
       </c>
       <c r="T115" s="14" t="inlineStr">
@@ -15037,7 +15039,7 @@
       </c>
       <c r="P116" s="14" t="inlineStr">
         <is>
-          <t>$432895.86820498994</t>
+          <t>$432895.8682049899</t>
         </is>
       </c>
       <c r="Q116" s="14" t="inlineStr">
@@ -15052,7 +15054,7 @@
       </c>
       <c r="S116" s="14" t="inlineStr">
         <is>
-          <t>$348379.4892357474</t>
+          <t>$348379.48923574743</t>
         </is>
       </c>
       <c r="T116" s="14" t="inlineStr">
@@ -15192,7 +15194,7 @@
       </c>
       <c r="S117" s="14" t="inlineStr">
         <is>
-          <t>$10378.969754481373</t>
+          <t>$10378.969754481372</t>
         </is>
       </c>
       <c r="T117" s="14" t="inlineStr">
@@ -15305,7 +15307,7 @@
         <v>3.374522871999913</v>
       </c>
       <c r="M118" s="14" t="n">
-        <v>3.04952870207474</v>
+        <v>3.049528702074739</v>
       </c>
       <c r="N118" s="14" t="n">
         <v>2.756533789479998</v>
@@ -15332,7 +15334,7 @@
       </c>
       <c r="S118" s="14" t="inlineStr">
         <is>
-          <t>$21990.150250849467</t>
+          <t>$21990.150250849463</t>
         </is>
       </c>
       <c r="T118" s="14" t="inlineStr">
@@ -15472,7 +15474,7 @@
       </c>
       <c r="S119" s="14" t="inlineStr">
         <is>
-          <t>$396.91618478638424</t>
+          <t>$396.9161847863842</t>
         </is>
       </c>
       <c r="T119" s="14" t="inlineStr">
@@ -15585,7 +15587,7 @@
         <v>3.810488180061373</v>
       </c>
       <c r="M120" s="14" t="n">
-        <v>4.001499712889237</v>
+        <v>4.001499712889236</v>
       </c>
       <c r="N120" s="14" t="n">
         <v>4.203153078402154</v>
@@ -15612,7 +15614,7 @@
       </c>
       <c r="S120" s="14" t="inlineStr">
         <is>
-          <t>$70950.6444424486</t>
+          <t>$70950.64444244858</t>
         </is>
       </c>
       <c r="T120" s="14" t="inlineStr">
@@ -15725,7 +15727,7 @@
         <v>3.810488180061373</v>
       </c>
       <c r="M121" s="14" t="n">
-        <v>4.001499712889237</v>
+        <v>4.001499712889236</v>
       </c>
       <c r="N121" s="14" t="n">
         <v>4.203153078402154</v>
@@ -15752,7 +15754,7 @@
       </c>
       <c r="S121" s="14" t="inlineStr">
         <is>
-          <t>$79819.59516279104</t>
+          <t>$79819.59516279103</t>
         </is>
       </c>
       <c r="T121" s="14" t="inlineStr">
@@ -16017,7 +16019,7 @@
       </c>
       <c r="P123" s="14" t="inlineStr">
         <is>
-          <t>$119807.52849959266</t>
+          <t>$119807.52849959263</t>
         </is>
       </c>
       <c r="Q123" s="14" t="inlineStr">
@@ -16032,7 +16034,7 @@
       </c>
       <c r="S123" s="14" t="inlineStr">
         <is>
-          <t>$105989.55423565996</t>
+          <t>$105989.55423565999</t>
         </is>
       </c>
       <c r="T123" s="14" t="inlineStr">
@@ -16157,7 +16159,7 @@
       </c>
       <c r="P124" s="14" t="inlineStr">
         <is>
-          <t>$275474.88586876425</t>
+          <t>$275474.8858687642</t>
         </is>
       </c>
       <c r="Q124" s="14" t="inlineStr">
@@ -16172,7 +16174,7 @@
       </c>
       <c r="S124" s="14" t="inlineStr">
         <is>
-          <t>$269595.51740956306</t>
+          <t>$269595.5174095631</t>
         </is>
       </c>
       <c r="T124" s="14" t="inlineStr">
@@ -16297,7 +16299,7 @@
       </c>
       <c r="P125" s="14" t="inlineStr">
         <is>
-          <t>$104942.81780954149</t>
+          <t>$104942.81780954148</t>
         </is>
       </c>
       <c r="Q125" s="14" t="inlineStr">
@@ -16312,7 +16314,7 @@
       </c>
       <c r="S125" s="14" t="inlineStr">
         <is>
-          <t>$102703.0583080418</t>
+          <t>$102703.05830804181</t>
         </is>
       </c>
       <c r="T125" s="14" t="inlineStr">
@@ -16437,7 +16439,7 @@
       </c>
       <c r="P126" s="14" t="inlineStr">
         <is>
-          <t>$31283.53646522382</t>
+          <t>$31283.536465223813</t>
         </is>
       </c>
       <c r="Q126" s="14" t="inlineStr">
@@ -16452,7 +16454,7 @@
       </c>
       <c r="S126" s="14" t="inlineStr">
         <is>
-          <t>$48817.781673074336</t>
+          <t>$48817.78167307435</t>
         </is>
       </c>
       <c r="T126" s="14" t="inlineStr">
@@ -16577,7 +16579,7 @@
       </c>
       <c r="P127" s="14" t="inlineStr">
         <is>
-          <t>$125134.14586089528</t>
+          <t>$125134.14586089525</t>
         </is>
       </c>
       <c r="Q127" s="14" t="inlineStr">
@@ -16592,7 +16594,7 @@
       </c>
       <c r="S127" s="14" t="inlineStr">
         <is>
-          <t>$195271.12669229734</t>
+          <t>$195271.1266922974</t>
         </is>
       </c>
       <c r="T127" s="14" t="inlineStr">
@@ -16717,7 +16719,7 @@
       </c>
       <c r="P128" s="14" t="inlineStr">
         <is>
-          <t>$17211.45997425914</t>
+          <t>$17211.459974259138</t>
         </is>
       </c>
       <c r="Q128" s="14" t="inlineStr">
@@ -16732,7 +16734,7 @@
       </c>
       <c r="S128" s="14" t="inlineStr">
         <is>
-          <t>$26719.235960807386</t>
+          <t>$26719.235960807393</t>
         </is>
       </c>
       <c r="T128" s="14" t="inlineStr">
@@ -16857,7 +16859,7 @@
       </c>
       <c r="P129" s="14" t="inlineStr">
         <is>
-          <t>$68844.68430015365</t>
+          <t>$68844.68430015363</t>
         </is>
       </c>
       <c r="Q129" s="14" t="inlineStr">
@@ -16872,7 +16874,7 @@
       </c>
       <c r="S129" s="14" t="inlineStr">
         <is>
-          <t>$106875.14988351685</t>
+          <t>$106875.14988351686</t>
         </is>
       </c>
       <c r="T129" s="14" t="inlineStr">
@@ -16997,7 +16999,7 @@
       </c>
       <c r="P130" s="14" t="inlineStr">
         <is>
-          <t>$156449.81702612274</t>
+          <t>$156449.81702612268</t>
         </is>
       </c>
       <c r="Q130" s="14" t="inlineStr">
@@ -17012,7 +17014,7 @@
       </c>
       <c r="S130" s="14" t="inlineStr">
         <is>
-          <t>$242790.05700815847</t>
+          <t>$242790.05700815853</t>
         </is>
       </c>
       <c r="T130" s="14" t="inlineStr">
@@ -17137,7 +17139,7 @@
       </c>
       <c r="P131" s="14" t="inlineStr">
         <is>
-          <t>$15389.474308378929</t>
+          <t>$15389.474308378925</t>
         </is>
       </c>
       <c r="Q131" s="14" t="inlineStr">
@@ -17152,7 +17154,7 @@
       </c>
       <c r="S131" s="14" t="inlineStr">
         <is>
-          <t>$22637.22864997408</t>
+          <t>$22637.228649974088</t>
         </is>
       </c>
       <c r="T131" s="14" t="inlineStr">
@@ -17277,7 +17279,7 @@
       </c>
       <c r="P132" s="14" t="inlineStr">
         <is>
-          <t>$3129.303831825166</t>
+          <t>$3129.303831825165</t>
         </is>
       </c>
       <c r="Q132" s="14" t="inlineStr">
@@ -17292,7 +17294,7 @@
       </c>
       <c r="S132" s="14" t="inlineStr">
         <is>
-          <t>$4857.961358341676</t>
+          <t>$4857.961358341677</t>
         </is>
       </c>
       <c r="T132" s="14" t="inlineStr">
@@ -17417,7 +17419,7 @@
       </c>
       <c r="P133" s="14" t="inlineStr">
         <is>
-          <t>$206534.05290046093</t>
+          <t>$206534.0529004609</t>
         </is>
       </c>
       <c r="Q133" s="14" t="inlineStr">
@@ -17432,7 +17434,7 @@
       </c>
       <c r="S133" s="14" t="inlineStr">
         <is>
-          <t>$320625.44965055055</t>
+          <t>$320625.4496505506</t>
         </is>
       </c>
       <c r="T133" s="14" t="inlineStr">
@@ -17545,7 +17547,7 @@
         <v>5.080650906748497</v>
       </c>
       <c r="M134" s="14" t="n">
-        <v>5.335332950518983</v>
+        <v>5.335332950518982</v>
       </c>
       <c r="N134" s="14" t="n">
         <v>5.604204104536204</v>
@@ -17697,7 +17699,7 @@
       </c>
       <c r="P135" s="14" t="inlineStr">
         <is>
-          <t>$7889.483104274985</t>
+          <t>$7889.483104274983</t>
         </is>
       </c>
       <c r="Q135" s="14" t="inlineStr">
@@ -17712,7 +17714,7 @@
       </c>
       <c r="S135" s="14" t="inlineStr">
         <is>
-          <t>$11649.856061449795</t>
+          <t>$11649.856061449796</t>
         </is>
       </c>
       <c r="T135" s="14" t="inlineStr">
@@ -17837,7 +17839,7 @@
       </c>
       <c r="P136" s="14" t="inlineStr">
         <is>
-          <t>$17175.238985915246</t>
+          <t>$17175.238985915243</t>
         </is>
       </c>
       <c r="Q136" s="14" t="inlineStr">
@@ -17852,7 +17854,7 @@
       </c>
       <c r="S136" s="14" t="inlineStr">
         <is>
-          <t>$21261.67123333946</t>
+          <t>$21261.671233339468</t>
         </is>
       </c>
       <c r="T136" s="14" t="inlineStr">
@@ -17977,7 +17979,7 @@
       </c>
       <c r="P137" s="14" t="inlineStr">
         <is>
-          <t>$25924.04192615178</t>
+          <t>$25924.041926151778</t>
         </is>
       </c>
       <c r="Q137" s="14" t="inlineStr">
@@ -17992,7 +17994,7 @@
       </c>
       <c r="S137" s="14" t="inlineStr">
         <is>
-          <t>$30706.189533382603</t>
+          <t>$30706.189533382607</t>
         </is>
       </c>
       <c r="T137" s="14" t="inlineStr">
@@ -18117,7 +18119,7 @@
       </c>
       <c r="P138" s="14" t="inlineStr">
         <is>
-          <t>$260842.80475259255</t>
+          <t>$260842.8047525925</t>
         </is>
       </c>
       <c r="Q138" s="14" t="inlineStr">
@@ -18132,7 +18134,7 @@
       </c>
       <c r="S138" s="14" t="inlineStr">
         <is>
-          <t>$350147.3795829512</t>
+          <t>$350147.37958295125</t>
         </is>
       </c>
       <c r="T138" s="14" t="inlineStr">
@@ -18257,7 +18259,7 @@
       </c>
       <c r="P139" s="14" t="inlineStr">
         <is>
-          <t>$49741.65881654348</t>
+          <t>$49741.658816543466</t>
         </is>
       </c>
       <c r="Q139" s="14" t="inlineStr">
@@ -18272,7 +18274,7 @@
       </c>
       <c r="S139" s="14" t="inlineStr">
         <is>
-          <t>$52579.48902014871</t>
+          <t>$52579.48902014872</t>
         </is>
       </c>
       <c r="T139" s="14" t="inlineStr">
@@ -18397,7 +18399,7 @@
       </c>
       <c r="P140" s="14" t="inlineStr">
         <is>
-          <t>$7380.80428154638</t>
+          <t>$7380.804281546379</t>
         </is>
       </c>
       <c r="Q140" s="14" t="inlineStr">
@@ -18412,7 +18414,7 @@
       </c>
       <c r="S140" s="14" t="inlineStr">
         <is>
-          <t>$8531.487300625917</t>
+          <t>$8531.487300625919</t>
         </is>
       </c>
       <c r="T140" s="14" t="inlineStr">
@@ -18537,7 +18539,7 @@
       </c>
       <c r="P141" s="14" t="inlineStr">
         <is>
-          <t>$63966.970440068624</t>
+          <t>$63966.97044006861</t>
         </is>
       </c>
       <c r="Q141" s="14" t="inlineStr">
@@ -18552,7 +18554,7 @@
       </c>
       <c r="S141" s="14" t="inlineStr">
         <is>
-          <t>$73939.55660542462</t>
+          <t>$73939.55660542463</t>
         </is>
       </c>
       <c r="T141" s="14" t="inlineStr">
@@ -18677,7 +18679,7 @@
       </c>
       <c r="P142" s="14" t="inlineStr">
         <is>
-          <t>$99798.3785258861</t>
+          <t>$99798.37852588607</t>
         </is>
       </c>
       <c r="Q142" s="14" t="inlineStr">
@@ -18692,7 +18694,7 @@
       </c>
       <c r="S142" s="14" t="inlineStr">
         <is>
-          <t>$156006.87900063326</t>
+          <t>$156006.8790006333</t>
         </is>
       </c>
       <c r="T142" s="14" t="inlineStr">
@@ -18817,7 +18819,7 @@
       </c>
       <c r="P143" s="14" t="inlineStr">
         <is>
-          <t>$119346.85370375315</t>
+          <t>$119346.85370375314</t>
         </is>
       </c>
       <c r="Q143" s="14" t="inlineStr">
@@ -18832,7 +18834,7 @@
       </c>
       <c r="S143" s="14" t="inlineStr">
         <is>
-          <t>$202027.48584497496</t>
+          <t>$202027.48584497502</t>
         </is>
       </c>
       <c r="T143" s="14" t="inlineStr">
@@ -18957,7 +18959,7 @@
       </c>
       <c r="P144" s="14" t="inlineStr">
         <is>
-          <t>$54467.582486869316</t>
+          <t>$54467.58248686931</t>
         </is>
       </c>
       <c r="Q144" s="14" t="inlineStr">
@@ -18972,7 +18974,7 @@
       </c>
       <c r="S144" s="14" t="inlineStr">
         <is>
-          <t>$84601.84212598501</t>
+          <t>$84601.84212598503</t>
         </is>
       </c>
       <c r="T144" s="14" t="inlineStr">
@@ -19097,7 +19099,7 @@
       </c>
       <c r="P145" s="14" t="inlineStr">
         <is>
-          <t>$84727.35053513004</t>
+          <t>$84727.35053513003</t>
         </is>
       </c>
       <c r="Q145" s="14" t="inlineStr">
@@ -19112,7 +19114,7 @@
       </c>
       <c r="S145" s="14" t="inlineStr">
         <is>
-          <t>$131602.86552931005</t>
+          <t>$131602.86552931007</t>
         </is>
       </c>
       <c r="T145" s="14" t="inlineStr">
@@ -19237,7 +19239,7 @@
       </c>
       <c r="P146" s="14" t="inlineStr">
         <is>
-          <t>$1265735.7871190028</t>
+          <t>$1265735.7871190025</t>
         </is>
       </c>
       <c r="Q146" s="14" t="inlineStr">
@@ -19252,7 +19254,7 @@
       </c>
       <c r="S146" s="14" t="inlineStr">
         <is>
-          <t>$1612447.1624701398</t>
+          <t>$1612447.1624701403</t>
         </is>
       </c>
       <c r="T146" s="14" t="inlineStr">
@@ -19377,7 +19379,7 @@
       </c>
       <c r="P147" s="14" t="inlineStr">
         <is>
-          <t>$8767.217128894568</t>
+          <t>$8767.217128894566</t>
         </is>
       </c>
       <c r="Q147" s="14" t="inlineStr">
@@ -19392,7 +19394,7 @@
       </c>
       <c r="S147" s="14" t="inlineStr">
         <is>
-          <t>$7912.95285307046</t>
+          <t>$7912.952853070462</t>
         </is>
       </c>
       <c r="T147" s="14" t="inlineStr">
@@ -19517,7 +19519,7 @@
       </c>
       <c r="P148" s="14" t="inlineStr">
         <is>
-          <t>$17534.434257789137</t>
+          <t>$17534.434257789133</t>
         </is>
       </c>
       <c r="Q148" s="14" t="inlineStr">
@@ -19532,7 +19534,7 @@
       </c>
       <c r="S148" s="14" t="inlineStr">
         <is>
-          <t>$15825.90570614092</t>
+          <t>$15825.905706140924</t>
         </is>
       </c>
       <c r="T148" s="14" t="inlineStr">
@@ -19657,7 +19659,7 @@
       </c>
       <c r="P149" s="14" t="inlineStr">
         <is>
-          <t>$8767.217128894568</t>
+          <t>$8767.217128894566</t>
         </is>
       </c>
       <c r="Q149" s="14" t="inlineStr">
@@ -19672,7 +19674,7 @@
       </c>
       <c r="S149" s="14" t="inlineStr">
         <is>
-          <t>$7912.95285307046</t>
+          <t>$7912.952853070462</t>
         </is>
       </c>
       <c r="T149" s="14" t="inlineStr">
@@ -19797,7 +19799,7 @@
       </c>
       <c r="P150" s="14" t="inlineStr">
         <is>
-          <t>$8767.217128894568</t>
+          <t>$8767.217128894566</t>
         </is>
       </c>
       <c r="Q150" s="14" t="inlineStr">
@@ -19812,7 +19814,7 @@
       </c>
       <c r="S150" s="14" t="inlineStr">
         <is>
-          <t>$7912.95285307046</t>
+          <t>$7912.952853070462</t>
         </is>
       </c>
       <c r="T150" s="14" t="inlineStr">
@@ -19937,7 +19939,7 @@
       </c>
       <c r="P151" s="14" t="inlineStr">
         <is>
-          <t>$96439.38841784025</t>
+          <t>$96439.38841784024</t>
         </is>
       </c>
       <c r="Q151" s="14" t="inlineStr">
@@ -19952,7 +19954,7 @@
       </c>
       <c r="S151" s="14" t="inlineStr">
         <is>
-          <t>$87042.48138377507</t>
+          <t>$87042.48138377508</t>
         </is>
       </c>
       <c r="T151" s="14" t="inlineStr">
@@ -20077,7 +20079,7 @@
       </c>
       <c r="P152" s="14" t="inlineStr">
         <is>
-          <t>$1137836.503037833</t>
+          <t>$1137836.5030378327</t>
         </is>
       </c>
       <c r="Q152" s="14" t="inlineStr">
@@ -20092,7 +20094,7 @@
       </c>
       <c r="S152" s="14" t="inlineStr">
         <is>
-          <t>$1518260.6219518196</t>
+          <t>$1518260.6219518199</t>
         </is>
       </c>
       <c r="T152" s="14" t="inlineStr">
@@ -20217,7 +20219,7 @@
       </c>
       <c r="P153" s="14" t="inlineStr">
         <is>
-          <t>$12761.331748147715</t>
+          <t>$12761.331748147712</t>
         </is>
       </c>
       <c r="Q153" s="14" t="inlineStr">
@@ -20232,7 +20234,7 @@
       </c>
       <c r="S153" s="14" t="inlineStr">
         <is>
-          <t>$18594.84521318747</t>
+          <t>$18594.845213187473</t>
         </is>
       </c>
       <c r="T153" s="14" t="inlineStr">
@@ -20357,7 +20359,7 @@
       </c>
       <c r="P154" s="14" t="inlineStr">
         <is>
-          <t>$42112.993900547626</t>
+          <t>$42112.99390054762</t>
         </is>
       </c>
       <c r="Q154" s="14" t="inlineStr">
@@ -20372,7 +20374,7 @@
       </c>
       <c r="S154" s="14" t="inlineStr">
         <is>
-          <t>$61364.329631536515</t>
+          <t>$61364.32963153653</t>
         </is>
       </c>
       <c r="T154" s="14" t="inlineStr">
@@ -20497,7 +20499,7 @@
       </c>
       <c r="P155" s="14" t="inlineStr">
         <is>
-          <t>$48275.044870515776</t>
+          <t>$48275.04487051576</t>
         </is>
       </c>
       <c r="Q155" s="14" t="inlineStr">
@@ -20512,7 +20514,7 @@
       </c>
       <c r="S155" s="14" t="inlineStr">
         <is>
-          <t>$59590.33996827676</t>
+          <t>$59590.33996827678</t>
         </is>
       </c>
       <c r="T155" s="14" t="inlineStr">
@@ -20637,7 +20639,7 @@
       </c>
       <c r="P156" s="14" t="inlineStr">
         <is>
-          <t>$67454.86517535547</t>
+          <t>$67454.86517535546</t>
         </is>
       </c>
       <c r="Q156" s="14" t="inlineStr">
@@ -20652,7 +20654,7 @@
       </c>
       <c r="S156" s="14" t="inlineStr">
         <is>
-          <t>$83504.11703870799</t>
+          <t>$83504.117038708</t>
         </is>
       </c>
       <c r="T156" s="14" t="inlineStr">
@@ -20777,7 +20779,7 @@
       </c>
       <c r="P157" s="14" t="inlineStr">
         <is>
-          <t>$76117.40849454912</t>
+          <t>$76117.4084945491</t>
         </is>
       </c>
       <c r="Q157" s="14" t="inlineStr">
@@ -20792,7 +20794,7 @@
       </c>
       <c r="S157" s="14" t="inlineStr">
         <is>
-          <t>$39566.56093484578</t>
+          <t>$39566.56093484579</t>
         </is>
       </c>
       <c r="T157" s="14" t="inlineStr">
@@ -20917,7 +20919,7 @@
       </c>
       <c r="P158" s="14" t="inlineStr">
         <is>
-          <t>$25372.469498183043</t>
+          <t>$25372.469498183036</t>
         </is>
       </c>
       <c r="Q158" s="14" t="inlineStr">
@@ -20932,7 +20934,7 @@
       </c>
       <c r="S158" s="14" t="inlineStr">
         <is>
-          <t>$13188.853644948591</t>
+          <t>$13188.853644948595</t>
         </is>
       </c>
       <c r="T158" s="14" t="inlineStr">
@@ -21057,7 +21059,7 @@
       </c>
       <c r="P159" s="14" t="inlineStr">
         <is>
-          <t>$279097.1644800135</t>
+          <t>$279097.1644800134</t>
         </is>
       </c>
       <c r="Q159" s="14" t="inlineStr">
@@ -21072,7 +21074,7 @@
       </c>
       <c r="S159" s="14" t="inlineStr">
         <is>
-          <t>$145077.39009443452</t>
+          <t>$145077.39009443455</t>
         </is>
       </c>
       <c r="T159" s="14" t="inlineStr">
@@ -21185,7 +21187,7 @@
         <v>8.89113908680987</v>
       </c>
       <c r="M160" s="14" t="n">
-        <v>9.33683266340822</v>
+        <v>9.336832663408218</v>
       </c>
       <c r="N160" s="14" t="n">
         <v>9.807357182938356</v>
@@ -21212,7 +21214,7 @@
       </c>
       <c r="S160" s="14" t="inlineStr">
         <is>
-          <t>$158312.62658580407</t>
+          <t>$158312.62658580404</t>
         </is>
       </c>
       <c r="T160" s="14" t="inlineStr">
@@ -21337,7 +21339,7 @@
       </c>
       <c r="P161" s="14" t="inlineStr">
         <is>
-          <t>$47233.362879712695</t>
+          <t>$47233.36287971269</t>
         </is>
       </c>
       <c r="Q161" s="14" t="inlineStr">
@@ -21352,7 +21354,7 @@
       </c>
       <c r="S161" s="14" t="inlineStr">
         <is>
-          <t>$60809.129131358684</t>
+          <t>$60809.12913135869</t>
         </is>
       </c>
       <c r="T161" s="14" t="inlineStr">
@@ -21465,7 +21467,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M162" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N162" s="14" t="n">
         <v>1.401051026134051</v>
@@ -21492,7 +21494,7 @@
       </c>
       <c r="S162" s="14" t="inlineStr">
         <is>
-          <t>$656.7901568747878</t>
+          <t>$656.7901568747877</t>
         </is>
       </c>
       <c r="T162" s="14" t="inlineStr">
@@ -21605,7 +21607,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M163" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N163" s="14" t="n">
         <v>1.401051026134051</v>
@@ -21757,7 +21759,7 @@
       </c>
       <c r="P164" s="14" t="inlineStr">
         <is>
-          <t>$20395.49601347112</t>
+          <t>$20395.496013471115</t>
         </is>
       </c>
       <c r="Q164" s="14" t="inlineStr">
@@ -21772,7 +21774,7 @@
       </c>
       <c r="S164" s="14" t="inlineStr">
         <is>
-          <t>$34042.59865267061</t>
+          <t>$34042.59865267062</t>
         </is>
       </c>
       <c r="T164" s="14" t="inlineStr">
@@ -21897,7 +21899,7 @@
       </c>
       <c r="P165" s="14" t="inlineStr">
         <is>
-          <t>$145315.0236782602</t>
+          <t>$145315.02367826016</t>
         </is>
       </c>
       <c r="Q165" s="14" t="inlineStr">
@@ -21912,7 +21914,7 @@
       </c>
       <c r="S165" s="14" t="inlineStr">
         <is>
-          <t>$225710.74629070755</t>
+          <t>$225710.7462907076</t>
         </is>
       </c>
       <c r="T165" s="14" t="inlineStr">
@@ -22177,7 +22179,7 @@
       </c>
       <c r="P167" s="14" t="inlineStr">
         <is>
-          <t>$22347.021100651156</t>
+          <t>$22347.02110065115</t>
         </is>
       </c>
       <c r="Q167" s="14" t="inlineStr">
@@ -22192,7 +22194,7 @@
       </c>
       <c r="S167" s="14" t="inlineStr">
         <is>
-          <t>$29502.887789876153</t>
+          <t>$29502.88778987616</t>
         </is>
       </c>
       <c r="T167" s="14" t="inlineStr">
@@ -22317,7 +22319,7 @@
       </c>
       <c r="P168" s="14" t="inlineStr">
         <is>
-          <t>$574360.6336644167</t>
+          <t>$574360.6336644166</t>
         </is>
       </c>
       <c r="Q168" s="14" t="inlineStr">
@@ -22332,7 +22334,7 @@
       </c>
       <c r="S168" s="14" t="inlineStr">
         <is>
-          <t>$719008.2327986198</t>
+          <t>$719008.2327986199</t>
         </is>
       </c>
       <c r="T168" s="14" t="inlineStr">
@@ -22457,7 +22459,7 @@
       </c>
       <c r="P169" s="14" t="inlineStr">
         <is>
-          <t>$38714.86714503022</t>
+          <t>$38714.86714503021</t>
         </is>
       </c>
       <c r="Q169" s="14" t="inlineStr">
@@ -22472,7 +22474,7 @@
       </c>
       <c r="S169" s="14" t="inlineStr">
         <is>
-          <t>$48464.86088607095</t>
+          <t>$48464.860886070965</t>
         </is>
       </c>
       <c r="T169" s="14" t="inlineStr">
@@ -23005,7 +23007,7 @@
         <v>0.8815292004664796</v>
       </c>
       <c r="M173" s="14" t="n">
-        <v>0.8964238022812293</v>
+        <v>0.8964238022812292</v>
       </c>
       <c r="N173" s="14" t="n">
         <v>0.9118015000900687</v>
@@ -23157,7 +23159,7 @@
       </c>
       <c r="P174" s="14" t="inlineStr">
         <is>
-          <t>$19450.546005347544</t>
+          <t>$19450.546005347536</t>
         </is>
       </c>
       <c r="Q174" s="14" t="inlineStr">
@@ -23172,7 +23174,7 @@
       </c>
       <c r="S174" s="14" t="inlineStr">
         <is>
-          <t>$23638.342683958268</t>
+          <t>$23638.342683958275</t>
         </is>
       </c>
       <c r="T174" s="14" t="inlineStr">
@@ -23297,7 +23299,7 @@
       </c>
       <c r="P175" s="14" t="inlineStr">
         <is>
-          <t>$38901.09201069509</t>
+          <t>$38901.09201069507</t>
         </is>
       </c>
       <c r="Q175" s="14" t="inlineStr">
@@ -23312,7 +23314,7 @@
       </c>
       <c r="S175" s="14" t="inlineStr">
         <is>
-          <t>$47276.685367916536</t>
+          <t>$47276.68536791655</t>
         </is>
       </c>
       <c r="T175" s="14" t="inlineStr">
@@ -23437,7 +23439,7 @@
       </c>
       <c r="P176" s="14" t="inlineStr">
         <is>
-          <t>$9291.515917658857</t>
+          <t>$9291.515917658855</t>
         </is>
       </c>
       <c r="Q176" s="14" t="inlineStr">
@@ -23452,7 +23454,7 @@
       </c>
       <c r="S176" s="14" t="inlineStr">
         <is>
-          <t>$14748.39651465027</t>
+          <t>$14748.396514650274</t>
         </is>
       </c>
       <c r="T176" s="14" t="inlineStr">
@@ -23577,7 +23579,7 @@
       </c>
       <c r="P177" s="14" t="inlineStr">
         <is>
-          <t>$27874.547752976574</t>
+          <t>$27874.547752976567</t>
         </is>
       </c>
       <c r="Q177" s="14" t="inlineStr">
@@ -23592,7 +23594,7 @@
       </c>
       <c r="S177" s="14" t="inlineStr">
         <is>
-          <t>$44245.18954395082</t>
+          <t>$44245.18954395083</t>
         </is>
       </c>
       <c r="T177" s="14" t="inlineStr">
@@ -24277,7 +24279,7 @@
       </c>
       <c r="P182" s="14" t="inlineStr">
         <is>
-          <t>$5907.953583235162</t>
+          <t>$5907.95358323516</t>
         </is>
       </c>
       <c r="Q182" s="14" t="inlineStr">
@@ -24292,7 +24294,7 @@
       </c>
       <c r="S182" s="14" t="inlineStr">
         <is>
-          <t>$8255.94895644279</t>
+          <t>$8255.948956442791</t>
         </is>
       </c>
       <c r="T182" s="14" t="inlineStr">
@@ -24837,7 +24839,7 @@
       </c>
       <c r="P186" s="14" t="inlineStr">
         <is>
-          <t>$271942.9756484432</t>
+          <t>$271942.97564844316</t>
         </is>
       </c>
       <c r="Q186" s="14" t="inlineStr">
@@ -24852,7 +24854,7 @@
       </c>
       <c r="S186" s="14" t="inlineStr">
         <is>
-          <t>$327901.8537665799</t>
+          <t>$327901.85376657994</t>
         </is>
       </c>
       <c r="T186" s="14" t="inlineStr">
@@ -24977,7 +24979,7 @@
       </c>
       <c r="P187" s="14" t="inlineStr">
         <is>
-          <t>$117878.87522812557</t>
+          <t>$117878.87522812556</t>
         </is>
       </c>
       <c r="Q187" s="14" t="inlineStr">
@@ -24992,7 +24994,7 @@
       </c>
       <c r="S187" s="14" t="inlineStr">
         <is>
-          <t>$139623.71666608725</t>
+          <t>$139623.71666608728</t>
         </is>
       </c>
       <c r="T187" s="14" t="inlineStr">
@@ -25117,7 +25119,7 @@
       </c>
       <c r="P188" s="14" t="inlineStr">
         <is>
-          <t>$5074.239661054146</t>
+          <t>$5074.2396610541455</t>
         </is>
       </c>
       <c r="Q188" s="14" t="inlineStr">
@@ -25132,7 +25134,7 @@
       </c>
       <c r="S188" s="14" t="inlineStr">
         <is>
-          <t>$5818.734775960387</t>
+          <t>$5818.734775960388</t>
         </is>
       </c>
       <c r="T188" s="14" t="inlineStr">
@@ -25257,7 +25259,7 @@
       </c>
       <c r="P189" s="14" t="inlineStr">
         <is>
-          <t>$5315.870121104349</t>
+          <t>$5315.870121104347</t>
         </is>
       </c>
       <c r="Q189" s="14" t="inlineStr">
@@ -25272,7 +25274,7 @@
       </c>
       <c r="S189" s="14" t="inlineStr">
         <is>
-          <t>$6095.817384339443</t>
+          <t>$6095.817384339444</t>
         </is>
       </c>
       <c r="T189" s="14" t="inlineStr">
@@ -25397,7 +25399,7 @@
       </c>
       <c r="P190" s="14" t="inlineStr">
         <is>
-          <t>$483.2613492199758</t>
+          <t>$483.26134921997567</t>
         </is>
       </c>
       <c r="Q190" s="14" t="inlineStr">
@@ -25412,7 +25414,7 @@
       </c>
       <c r="S190" s="14" t="inlineStr">
         <is>
-          <t>$554.1657088383633</t>
+          <t>$554.1657088383635</t>
         </is>
       </c>
       <c r="T190" s="14" t="inlineStr">
@@ -25537,7 +25539,7 @@
       </c>
       <c r="P191" s="14" t="inlineStr">
         <is>
-          <t>$2800.905394548149</t>
+          <t>$2800.9053945481487</t>
         </is>
       </c>
       <c r="Q191" s="14" t="inlineStr">
@@ -25552,7 +25554,7 @@
       </c>
       <c r="S191" s="14" t="inlineStr">
         <is>
-          <t>$3082.721636626368</t>
+          <t>$3082.7216366263683</t>
         </is>
       </c>
       <c r="T191" s="14" t="inlineStr">
@@ -25677,7 +25679,7 @@
       </c>
       <c r="P192" s="14" t="inlineStr">
         <is>
-          <t>$724.8920238299627</t>
+          <t>$724.8920238299626</t>
         </is>
       </c>
       <c r="Q192" s="14" t="inlineStr">
@@ -25692,7 +25694,7 @@
       </c>
       <c r="S192" s="14" t="inlineStr">
         <is>
-          <t>$831.2485632575449</t>
+          <t>$831.248563257545</t>
         </is>
       </c>
       <c r="T192" s="14" t="inlineStr">
@@ -26112,7 +26114,7 @@
       </c>
       <c r="S195" s="14" t="inlineStr">
         <is>
-          <t>$7311.703791183734</t>
+          <t>$7311.703791183733</t>
         </is>
       </c>
       <c r="T195" s="14" t="inlineStr">
@@ -26252,7 +26254,7 @@
       </c>
       <c r="S196" s="14" t="inlineStr">
         <is>
-          <t>$78057.96225777293</t>
+          <t>$78057.96225777292</t>
         </is>
       </c>
       <c r="T196" s="14" t="inlineStr">
@@ -26377,7 +26379,7 @@
       </c>
       <c r="P197" s="14" t="inlineStr">
         <is>
-          <t>$4228.894537667144</t>
+          <t>$4228.894537667143</t>
         </is>
       </c>
       <c r="Q197" s="14" t="inlineStr">
@@ -26392,7 +26394,7 @@
       </c>
       <c r="S197" s="14" t="inlineStr">
         <is>
-          <t>$3217.47071327471</t>
+          <t>$3217.4707132747108</t>
         </is>
       </c>
       <c r="T197" s="14" t="inlineStr">
@@ -26517,7 +26519,7 @@
       </c>
       <c r="P198" s="14" t="inlineStr">
         <is>
-          <t>$1021934.3281762959</t>
+          <t>$1021934.3281762956</t>
         </is>
       </c>
       <c r="Q198" s="14" t="inlineStr">
@@ -26532,7 +26534,7 @@
       </c>
       <c r="S198" s="14" t="inlineStr">
         <is>
-          <t>$1379998.9979299435</t>
+          <t>$1379998.9979299437</t>
         </is>
       </c>
       <c r="T198" s="14" t="inlineStr">
@@ -26657,7 +26659,7 @@
       </c>
       <c r="P199" s="14" t="inlineStr">
         <is>
-          <t>$403023.6223609859</t>
+          <t>$403023.62236098584</t>
         </is>
       </c>
       <c r="Q199" s="14" t="inlineStr">
@@ -26672,7 +26674,7 @@
       </c>
       <c r="S199" s="14" t="inlineStr">
         <is>
-          <t>$507065.2460350961</t>
+          <t>$507065.24603509624</t>
         </is>
       </c>
       <c r="T199" s="14" t="inlineStr">
@@ -26812,7 +26814,7 @@
       </c>
       <c r="S200" s="14" t="inlineStr">
         <is>
-          <t>$29163.22361761568</t>
+          <t>$29163.223617615677</t>
         </is>
       </c>
       <c r="T200" s="14" t="inlineStr">
@@ -26925,7 +26927,7 @@
         <v>8.89113908680987</v>
       </c>
       <c r="M201" s="14" t="n">
-        <v>9.33683266340822</v>
+        <v>9.336832663408218</v>
       </c>
       <c r="N201" s="14" t="n">
         <v>9.807357182938356</v>
@@ -26952,7 +26954,7 @@
       </c>
       <c r="S201" s="14" t="inlineStr">
         <is>
-          <t>$35919.04361588027</t>
+          <t>$35919.04361588026</t>
         </is>
       </c>
       <c r="T201" s="14" t="inlineStr">
@@ -27092,7 +27094,7 @@
       </c>
       <c r="S202" s="14" t="inlineStr">
         <is>
-          <t>$220404.1424409511</t>
+          <t>$220404.14244095108</t>
         </is>
       </c>
       <c r="T202" s="14" t="inlineStr">
@@ -27485,7 +27487,7 @@
         <v>7.620976360122746</v>
       </c>
       <c r="M205" s="14" t="n">
-        <v>8.002999425778475</v>
+        <v>8.002999425778473</v>
       </c>
       <c r="N205" s="14" t="n">
         <v>8.406306156804307</v>
@@ -27652,7 +27654,7 @@
       </c>
       <c r="S206" s="14" t="inlineStr">
         <is>
-          <t>$38495.626887608385</t>
+          <t>$38495.62688760838</t>
         </is>
       </c>
       <c r="T206" s="14" t="inlineStr">
@@ -27792,7 +27794,7 @@
       </c>
       <c r="S207" s="14" t="inlineStr">
         <is>
-          <t>$11749.767440283444</t>
+          <t>$11749.767440283442</t>
         </is>
       </c>
       <c r="T207" s="14" t="inlineStr">
@@ -27917,7 +27919,7 @@
       </c>
       <c r="P208" s="14" t="inlineStr">
         <is>
-          <t>$164238.25507785575</t>
+          <t>$164238.25507785572</t>
         </is>
       </c>
       <c r="Q208" s="14" t="inlineStr">
@@ -27932,7 +27934,7 @@
       </c>
       <c r="S208" s="14" t="inlineStr">
         <is>
-          <t>$205600.1937111414</t>
+          <t>$205600.19371114142</t>
         </is>
       </c>
       <c r="T208" s="14" t="inlineStr">
@@ -28337,7 +28339,7 @@
       </c>
       <c r="P211" s="14" t="inlineStr">
         <is>
-          <t>$407375.00194548245</t>
+          <t>$407375.00194548233</t>
         </is>
       </c>
       <c r="Q211" s="14" t="inlineStr">
@@ -28352,7 +28354,7 @@
       </c>
       <c r="S211" s="14" t="inlineStr">
         <is>
-          <t>$599230.4142775438</t>
+          <t>$599230.4142775439</t>
         </is>
       </c>
       <c r="T211" s="14" t="inlineStr">
@@ -28477,7 +28479,7 @@
       </c>
       <c r="P212" s="14" t="inlineStr">
         <is>
-          <t>$77595.23846580618</t>
+          <t>$77595.23846580616</t>
         </is>
       </c>
       <c r="Q212" s="14" t="inlineStr">
@@ -28492,7 +28494,7 @@
       </c>
       <c r="S212" s="14" t="inlineStr">
         <is>
-          <t>$114139.12652905597</t>
+          <t>$114139.12652905598</t>
         </is>
       </c>
       <c r="T212" s="14" t="inlineStr">
@@ -28617,7 +28619,7 @@
       </c>
       <c r="P213" s="14" t="inlineStr">
         <is>
-          <t>$74140.67743489228</t>
+          <t>$74140.67743489226</t>
         </is>
       </c>
       <c r="Q213" s="14" t="inlineStr">
@@ -28632,7 +28634,7 @@
       </c>
       <c r="S213" s="14" t="inlineStr">
         <is>
-          <t>$50154.13704145925</t>
+          <t>$50154.13704145926</t>
         </is>
       </c>
       <c r="T213" s="14" t="inlineStr">
@@ -28757,7 +28759,7 @@
       </c>
       <c r="P214" s="14" t="inlineStr">
         <is>
-          <t>$40205.031653695216</t>
+          <t>$40205.03165369521</t>
         </is>
       </c>
       <c r="Q214" s="14" t="inlineStr">
@@ -28772,7 +28774,7 @@
       </c>
       <c r="S214" s="14" t="inlineStr">
         <is>
-          <t>$63817.3312048921</t>
+          <t>$63817.33120489211</t>
         </is>
       </c>
       <c r="T214" s="14" t="inlineStr">
@@ -28897,7 +28899,7 @@
       </c>
       <c r="P215" s="14" t="inlineStr">
         <is>
-          <t>$75597.07755313558</t>
+          <t>$75597.07755313556</t>
         </is>
       </c>
       <c r="Q215" s="14" t="inlineStr">
@@ -28912,7 +28914,7 @@
       </c>
       <c r="S215" s="14" t="inlineStr">
         <is>
-          <t>$103176.02645499578</t>
+          <t>$103176.02645499581</t>
         </is>
       </c>
       <c r="T215" s="14" t="inlineStr">
@@ -29037,7 +29039,7 @@
       </c>
       <c r="P216" s="14" t="inlineStr">
         <is>
-          <t>$226791.23265940673</t>
+          <t>$226791.2326594067</t>
         </is>
       </c>
       <c r="Q216" s="14" t="inlineStr">
@@ -29052,7 +29054,7 @@
       </c>
       <c r="S216" s="14" t="inlineStr">
         <is>
-          <t>$309528.0793649874</t>
+          <t>$309528.07936498744</t>
         </is>
       </c>
       <c r="T216" s="14" t="inlineStr">
@@ -29177,7 +29179,7 @@
       </c>
       <c r="P217" s="14" t="inlineStr">
         <is>
-          <t>$188992.69388283897</t>
+          <t>$188992.6938828389</t>
         </is>
       </c>
       <c r="Q217" s="14" t="inlineStr">
@@ -29192,7 +29194,7 @@
       </c>
       <c r="S217" s="14" t="inlineStr">
         <is>
-          <t>$257940.06613748948</t>
+          <t>$257940.06613748954</t>
         </is>
       </c>
       <c r="T217" s="14" t="inlineStr">
@@ -29317,7 +29319,7 @@
       </c>
       <c r="P218" s="14" t="inlineStr">
         <is>
-          <t>$114903.81079601085</t>
+          <t>$114903.81079601082</t>
         </is>
       </c>
       <c r="Q218" s="14" t="inlineStr">
@@ -29332,7 +29334,7 @@
       </c>
       <c r="S218" s="14" t="inlineStr">
         <is>
-          <t>$144566.53620035926</t>
+          <t>$144566.5362003593</t>
         </is>
       </c>
       <c r="T218" s="14" t="inlineStr">
@@ -29445,7 +29447,7 @@
         <v>8.89113908680987</v>
       </c>
       <c r="M219" s="14" t="n">
-        <v>9.33683266340822</v>
+        <v>9.336832663408218</v>
       </c>
       <c r="N219" s="14" t="n">
         <v>9.807357182938356</v>
@@ -29585,7 +29587,7 @@
         <v>8.89113908680987</v>
       </c>
       <c r="M220" s="14" t="n">
-        <v>9.33683266340822</v>
+        <v>9.336832663408218</v>
       </c>
       <c r="N220" s="14" t="n">
         <v>9.807357182938356</v>
@@ -29737,7 +29739,7 @@
       </c>
       <c r="P221" s="14" t="inlineStr">
         <is>
-          <t>$397057.2485079955</t>
+          <t>$397057.24850799545</t>
         </is>
       </c>
       <c r="Q221" s="14" t="inlineStr">
@@ -29752,7 +29754,7 @@
       </c>
       <c r="S221" s="14" t="inlineStr">
         <is>
-          <t>$375653.4249103627</t>
+          <t>$375653.42491036275</t>
         </is>
       </c>
       <c r="T221" s="14" t="inlineStr">
@@ -29877,7 +29879,7 @@
       </c>
       <c r="P222" s="14" t="inlineStr">
         <is>
-          <t>$30210.150384888373</t>
+          <t>$30210.150384888366</t>
         </is>
       </c>
       <c r="Q222" s="14" t="inlineStr">
@@ -29892,7 +29894,7 @@
       </c>
       <c r="S222" s="14" t="inlineStr">
         <is>
-          <t>$34315.4526228575</t>
+          <t>$34315.452622857505</t>
         </is>
       </c>
       <c r="T222" s="14" t="inlineStr">
@@ -30017,7 +30019,7 @@
       </c>
       <c r="P223" s="14" t="inlineStr">
         <is>
-          <t>$11036.385927729034</t>
+          <t>$11036.385927729032</t>
         </is>
       </c>
       <c r="Q223" s="14" t="inlineStr">
@@ -30032,7 +30034,7 @@
       </c>
       <c r="S223" s="14" t="inlineStr">
         <is>
-          <t>$13840.522547273906</t>
+          <t>$13840.522547273908</t>
         </is>
       </c>
       <c r="T223" s="14" t="inlineStr">
@@ -30157,7 +30159,7 @@
       </c>
       <c r="P224" s="14" t="inlineStr">
         <is>
-          <t>$38484.42360565239</t>
+          <t>$38484.42360565238</t>
         </is>
       </c>
       <c r="Q224" s="14" t="inlineStr">
@@ -30172,7 +30174,7 @@
       </c>
       <c r="S224" s="14" t="inlineStr">
         <is>
-          <t>$48837.836162806154</t>
+          <t>$48837.83616280617</t>
         </is>
       </c>
       <c r="T224" s="14" t="inlineStr">
@@ -30297,7 +30299,7 @@
       </c>
       <c r="P225" s="14" t="inlineStr">
         <is>
-          <t>$132519.27649550108</t>
+          <t>$132519.27649550105</t>
         </is>
       </c>
       <c r="Q225" s="14" t="inlineStr">
@@ -30312,7 +30314,7 @@
       </c>
       <c r="S225" s="14" t="inlineStr">
         <is>
-          <t>$177554.9475003276</t>
+          <t>$177554.94750032766</t>
         </is>
       </c>
       <c r="T225" s="14" t="inlineStr">
@@ -30437,7 +30439,7 @@
       </c>
       <c r="P226" s="14" t="inlineStr">
         <is>
-          <t>$79511.52919583225</t>
+          <t>$79511.52919583222</t>
         </is>
       </c>
       <c r="Q226" s="14" t="inlineStr">
@@ -30452,7 +30454,7 @@
       </c>
       <c r="S226" s="14" t="inlineStr">
         <is>
-          <t>$106533.12396934973</t>
+          <t>$106533.12396934975</t>
         </is>
       </c>
       <c r="T226" s="14" t="inlineStr">
@@ -30565,7 +30567,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M227" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N227" s="14" t="n">
         <v>1.401051026134051</v>
@@ -30592,7 +30594,7 @@
       </c>
       <c r="S227" s="14" t="inlineStr">
         <is>
-          <t>$15558.711213650187</t>
+          <t>$15558.711213650186</t>
         </is>
       </c>
       <c r="T227" s="14" t="inlineStr">
@@ -30857,7 +30859,7 @@
       </c>
       <c r="P229" s="14" t="inlineStr">
         <is>
-          <t>$4810.758250900936</t>
+          <t>$4810.758250900934</t>
         </is>
       </c>
       <c r="Q229" s="14" t="inlineStr">
@@ -30872,7 +30874,7 @@
       </c>
       <c r="S229" s="14" t="inlineStr">
         <is>
-          <t>$4705.267158342021</t>
+          <t>$4705.2671583420215</t>
         </is>
       </c>
       <c r="T229" s="14" t="inlineStr">
@@ -30985,7 +30987,7 @@
         <v>0.8523999504503074</v>
       </c>
       <c r="M230" s="14" t="n">
-        <v>0.834251923581804</v>
+        <v>0.8342519235818039</v>
       </c>
       <c r="N230" s="14" t="n">
         <v>0.8166975702698929</v>
@@ -31012,7 +31014,7 @@
       </c>
       <c r="S230" s="14" t="inlineStr">
         <is>
-          <t>$3164.0333999406103</t>
+          <t>$3164.03339994061</t>
         </is>
       </c>
       <c r="T230" s="14" t="inlineStr">
@@ -31137,7 +31139,7 @@
       </c>
       <c r="P231" s="14" t="inlineStr">
         <is>
-          <t>$201993.50567172945</t>
+          <t>$201993.5056717294</t>
         </is>
       </c>
       <c r="Q231" s="14" t="inlineStr">
@@ -31152,7 +31154,7 @@
       </c>
       <c r="S231" s="14" t="inlineStr">
         <is>
-          <t>$209077.03121633956</t>
+          <t>$209077.0312163396</t>
         </is>
       </c>
       <c r="T231" s="14" t="inlineStr">
@@ -31277,7 +31279,7 @@
       </c>
       <c r="P232" s="14" t="inlineStr">
         <is>
-          <t>$8480.75775468518</t>
+          <t>$8480.757754685179</t>
         </is>
       </c>
       <c r="Q232" s="14" t="inlineStr">
@@ -31292,7 +31294,7 @@
       </c>
       <c r="S232" s="14" t="inlineStr">
         <is>
-          <t>$9054.787674471709</t>
+          <t>$9054.78767447171</t>
         </is>
       </c>
       <c r="T232" s="14" t="inlineStr">
@@ -31417,7 +31419,7 @@
       </c>
       <c r="P233" s="14" t="inlineStr">
         <is>
-          <t>$54348.23338774189</t>
+          <t>$54348.233387741886</t>
         </is>
       </c>
       <c r="Q233" s="14" t="inlineStr">
@@ -31432,7 +31434,7 @@
       </c>
       <c r="S233" s="14" t="inlineStr">
         <is>
-          <t>$58026.690300242786</t>
+          <t>$58026.6903002428</t>
         </is>
       </c>
       <c r="T233" s="14" t="inlineStr">
@@ -31557,7 +31559,7 @@
       </c>
       <c r="P234" s="14" t="inlineStr">
         <is>
-          <t>$42719.316190160476</t>
+          <t>$42719.31619016047</t>
         </is>
       </c>
       <c r="Q234" s="14" t="inlineStr">
@@ -31572,7 +31574,7 @@
       </c>
       <c r="S234" s="14" t="inlineStr">
         <is>
-          <t>$45610.73541737253</t>
+          <t>$45610.73541737254</t>
         </is>
       </c>
       <c r="T234" s="14" t="inlineStr">
@@ -31697,7 +31699,7 @@
       </c>
       <c r="P235" s="14" t="inlineStr">
         <is>
-          <t>$207269.3772133956</t>
+          <t>$207269.37721339555</t>
         </is>
       </c>
       <c r="Q235" s="14" t="inlineStr">
@@ -31712,7 +31714,7 @@
       </c>
       <c r="S235" s="14" t="inlineStr">
         <is>
-          <t>$221298.2221466653</t>
+          <t>$221298.22214666536</t>
         </is>
       </c>
       <c r="T235" s="14" t="inlineStr">
@@ -31837,7 +31839,7 @@
       </c>
       <c r="P236" s="14" t="inlineStr">
         <is>
-          <t>$29910.38799569627</t>
+          <t>$29910.387995696263</t>
         </is>
       </c>
       <c r="Q236" s="14" t="inlineStr">
@@ -31852,7 +31854,7 @@
       </c>
       <c r="S236" s="14" t="inlineStr">
         <is>
-          <t>$32214.279097088413</t>
+          <t>$32214.27909708842</t>
         </is>
       </c>
       <c r="T236" s="14" t="inlineStr">
@@ -31977,7 +31979,7 @@
       </c>
       <c r="P237" s="14" t="inlineStr">
         <is>
-          <t>$59820.77874856421</t>
+          <t>$59820.7787485642</t>
         </is>
       </c>
       <c r="Q237" s="14" t="inlineStr">
@@ -31992,7 +31994,7 @@
       </c>
       <c r="S237" s="14" t="inlineStr">
         <is>
-          <t>$64428.56116372365</t>
+          <t>$64428.561163723665</t>
         </is>
       </c>
       <c r="T237" s="14" t="inlineStr">
@@ -32117,7 +32119,7 @@
       </c>
       <c r="P238" s="14" t="inlineStr">
         <is>
-          <t>$358924.6724913852</t>
+          <t>$358924.67249138514</t>
         </is>
       </c>
       <c r="Q238" s="14" t="inlineStr">
@@ -32132,7 +32134,7 @@
       </c>
       <c r="S238" s="14" t="inlineStr">
         <is>
-          <t>$386571.3669823419</t>
+          <t>$386571.366982342</t>
         </is>
       </c>
       <c r="T238" s="14" t="inlineStr">
@@ -32257,7 +32259,7 @@
       </c>
       <c r="P239" s="14" t="inlineStr">
         <is>
-          <t>$6587.635715114326</t>
+          <t>$6587.635715114324</t>
         </is>
       </c>
       <c r="Q239" s="14" t="inlineStr">
@@ -32272,7 +32274,7 @@
       </c>
       <c r="S239" s="14" t="inlineStr">
         <is>
-          <t>$8337.838295205951</t>
+          <t>$8337.838295205953</t>
         </is>
       </c>
       <c r="T239" s="14" t="inlineStr">
@@ -32397,7 +32399,7 @@
       </c>
       <c r="P240" s="14" t="inlineStr">
         <is>
-          <t>$22566.79194943079</t>
+          <t>$22566.791949430786</t>
         </is>
       </c>
       <c r="Q240" s="14" t="inlineStr">
@@ -32412,7 +32414,7 @@
       </c>
       <c r="S240" s="14" t="inlineStr">
         <is>
-          <t>$33491.20838707597</t>
+          <t>$33491.208387075974</t>
         </is>
       </c>
       <c r="T240" s="14" t="inlineStr">
@@ -32692,7 +32694,7 @@
       </c>
       <c r="S242" s="14" t="inlineStr">
         <is>
-          <t>$11749.767440283444</t>
+          <t>$11749.767440283442</t>
         </is>
       </c>
       <c r="T242" s="14" t="inlineStr">
@@ -32817,7 +32819,7 @@
       </c>
       <c r="P243" s="14" t="inlineStr">
         <is>
-          <t>$23044.87077327666</t>
+          <t>$23044.870773276656</t>
         </is>
       </c>
       <c r="Q243" s="14" t="inlineStr">
@@ -32832,7 +32834,7 @@
       </c>
       <c r="S243" s="14" t="inlineStr">
         <is>
-          <t>$32771.41437381562</t>
+          <t>$32771.41437381563</t>
         </is>
       </c>
       <c r="T243" s="14" t="inlineStr">
@@ -32945,7 +32947,7 @@
         <v>10.10223370380704</v>
       </c>
       <c r="M244" s="14" t="n">
-        <v>9.482141502620605</v>
+        <v>9.482141502620603</v>
       </c>
       <c r="N244" s="14" t="n">
         <v>8.902371195744488</v>
@@ -33112,7 +33114,7 @@
       </c>
       <c r="S245" s="14" t="inlineStr">
         <is>
-          <t>$128509.49577884223</t>
+          <t>$128509.49577884222</t>
         </is>
       </c>
       <c r="T245" s="14" t="inlineStr">
@@ -33377,7 +33379,7 @@
       </c>
       <c r="P247" s="14" t="inlineStr">
         <is>
-          <t>$85426.47470863111</t>
+          <t>$85426.4747086311</t>
         </is>
       </c>
       <c r="Q247" s="14" t="inlineStr">
@@ -33392,7 +33394,7 @@
       </c>
       <c r="S247" s="14" t="inlineStr">
         <is>
-          <t>$71838.41101140456</t>
+          <t>$71838.41101140458</t>
         </is>
       </c>
       <c r="T247" s="14" t="inlineStr">
@@ -34232,7 +34234,7 @@
       </c>
       <c r="S253" s="14" t="inlineStr">
         <is>
-          <t>$283803.00502325705</t>
+          <t>$283803.005023257</t>
         </is>
       </c>
       <c r="T253" s="14" t="inlineStr">
@@ -34485,7 +34487,7 @@
         <v>14.16079616270661</v>
       </c>
       <c r="M255" s="14" t="n">
-        <v>15.10798585669276</v>
+        <v>15.10798585669275</v>
       </c>
       <c r="N255" s="14" t="n">
         <v>16.12262355127993</v>
@@ -34652,7 +34654,7 @@
       </c>
       <c r="S256" s="14" t="inlineStr">
         <is>
-          <t>$524917.1937239405</t>
+          <t>$524917.1937239404</t>
         </is>
       </c>
       <c r="T256" s="14" t="inlineStr">
@@ -34777,7 +34779,7 @@
       </c>
       <c r="P257" s="14" t="inlineStr">
         <is>
-          <t>$62669.98649576708</t>
+          <t>$62669.986495767065</t>
         </is>
       </c>
       <c r="Q257" s="14" t="inlineStr">
@@ -34792,7 +34794,7 @@
       </c>
       <c r="S257" s="14" t="inlineStr">
         <is>
-          <t>$93482.96661429577</t>
+          <t>$93482.96661429579</t>
         </is>
       </c>
       <c r="T257" s="14" t="inlineStr">
@@ -34917,7 +34919,7 @@
       </c>
       <c r="P258" s="14" t="inlineStr">
         <is>
-          <t>$19941.976225104616</t>
+          <t>$19941.976225104612</t>
         </is>
       </c>
       <c r="Q258" s="14" t="inlineStr">
@@ -34932,7 +34934,7 @@
       </c>
       <c r="S258" s="14" t="inlineStr">
         <is>
-          <t>$19333.422706570207</t>
+          <t>$19333.42270657021</t>
         </is>
       </c>
       <c r="T258" s="14" t="inlineStr">
@@ -35057,7 +35059,7 @@
       </c>
       <c r="P259" s="14" t="inlineStr">
         <is>
-          <t>$185163.0112432818</t>
+          <t>$185163.01124328177</t>
         </is>
       </c>
       <c r="Q259" s="14" t="inlineStr">
@@ -35072,7 +35074,7 @@
       </c>
       <c r="S259" s="14" t="inlineStr">
         <is>
-          <t>$294780.89745585964</t>
+          <t>$294780.89745585975</t>
         </is>
       </c>
       <c r="T259" s="14" t="inlineStr">
@@ -35197,7 +35199,7 @@
       </c>
       <c r="P260" s="14" t="inlineStr">
         <is>
-          <t>$412054.01905187883</t>
+          <t>$412054.0190518787</t>
         </is>
       </c>
       <c r="Q260" s="14" t="inlineStr">
@@ -35212,7 +35214,7 @@
       </c>
       <c r="S260" s="14" t="inlineStr">
         <is>
-          <t>$650559.4647666976</t>
+          <t>$650559.4647666977</t>
         </is>
       </c>
       <c r="T260" s="14" t="inlineStr">
@@ -35337,7 +35339,7 @@
       </c>
       <c r="P261" s="14" t="inlineStr">
         <is>
-          <t>$402247.42783833185</t>
+          <t>$402247.4278383318</t>
         </is>
       </c>
       <c r="Q261" s="14" t="inlineStr">
@@ -35352,7 +35354,7 @@
       </c>
       <c r="S261" s="14" t="inlineStr">
         <is>
-          <t>$633375.4903343185</t>
+          <t>$633375.4903343186</t>
         </is>
       </c>
       <c r="T261" s="14" t="inlineStr">
@@ -35477,7 +35479,7 @@
       </c>
       <c r="P262" s="14" t="inlineStr">
         <is>
-          <t>$252230.35734775796</t>
+          <t>$252230.3573477579</t>
         </is>
       </c>
       <c r="Q262" s="14" t="inlineStr">
@@ -35492,7 +35494,7 @@
       </c>
       <c r="S262" s="14" t="inlineStr">
         <is>
-          <t>$357361.49294471095</t>
+          <t>$357361.49294471106</t>
         </is>
       </c>
       <c r="T262" s="14" t="inlineStr">
@@ -35617,7 +35619,7 @@
       </c>
       <c r="P263" s="14" t="inlineStr">
         <is>
-          <t>$402078.5452063454</t>
+          <t>$402078.54520634527</t>
         </is>
       </c>
       <c r="Q263" s="14" t="inlineStr">
@@ -35632,7 +35634,7 @@
       </c>
       <c r="S263" s="14" t="inlineStr">
         <is>
-          <t>$403733.31707822933</t>
+          <t>$403733.3170782294</t>
         </is>
       </c>
       <c r="T263" s="14" t="inlineStr">
@@ -35757,7 +35759,7 @@
       </c>
       <c r="P264" s="14" t="inlineStr">
         <is>
-          <t>$335358.48789758637</t>
+          <t>$335358.4878975863</t>
         </is>
       </c>
       <c r="Q264" s="14" t="inlineStr">
@@ -35772,7 +35774,7 @@
       </c>
       <c r="S264" s="14" t="inlineStr">
         <is>
-          <t>$438867.9687137862</t>
+          <t>$438867.9687137863</t>
         </is>
       </c>
       <c r="T264" s="14" t="inlineStr">
@@ -35885,7 +35887,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M265" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N265" s="14" t="n">
         <v>1.401051026134051</v>
@@ -35912,7 +35914,7 @@
       </c>
       <c r="S265" s="14" t="inlineStr">
         <is>
-          <t>$17737.66111061215</t>
+          <t>$17737.661110612145</t>
         </is>
       </c>
       <c r="T265" s="14" t="inlineStr">
@@ -36052,7 +36054,7 @@
       </c>
       <c r="S266" s="14" t="inlineStr">
         <is>
-          <t>$92849.83173724196</t>
+          <t>$92849.83173724194</t>
         </is>
       </c>
       <c r="T266" s="14" t="inlineStr">
@@ -36177,7 +36179,7 @@
       </c>
       <c r="P267" s="14" t="inlineStr">
         <is>
-          <t>$255555.53653601868</t>
+          <t>$255555.53653601863</t>
         </is>
       </c>
       <c r="Q267" s="14" t="inlineStr">
@@ -36192,7 +36194,7 @@
       </c>
       <c r="S267" s="14" t="inlineStr">
         <is>
-          <t>$321527.8803017662</t>
+          <t>$321527.8803017663</t>
         </is>
       </c>
       <c r="T267" s="14" t="inlineStr">
@@ -36317,7 +36319,7 @@
       </c>
       <c r="P268" s="14" t="inlineStr">
         <is>
-          <t>$1539804.6187926873</t>
+          <t>$1539804.6187926868</t>
         </is>
       </c>
       <c r="Q268" s="14" t="inlineStr">
@@ -36332,7 +36334,7 @@
       </c>
       <c r="S268" s="14" t="inlineStr">
         <is>
-          <t>$1994444.0062693737</t>
+          <t>$1994444.0062693742</t>
         </is>
       </c>
       <c r="T268" s="14" t="inlineStr">
@@ -36457,7 +36459,7 @@
       </c>
       <c r="P269" s="14" t="inlineStr">
         <is>
-          <t>$35082.92425551471</t>
+          <t>$35082.9242555147</t>
         </is>
       </c>
       <c r="Q269" s="14" t="inlineStr">
@@ -36472,7 +36474,7 @@
       </c>
       <c r="S269" s="14" t="inlineStr">
         <is>
-          <t>$55687.024851391936</t>
+          <t>$55687.02485139195</t>
         </is>
       </c>
       <c r="T269" s="14" t="inlineStr">
@@ -36597,7 +36599,7 @@
       </c>
       <c r="P270" s="14" t="inlineStr">
         <is>
-          <t>$57807.16367395894</t>
+          <t>$57807.16367395892</t>
         </is>
       </c>
       <c r="Q270" s="14" t="inlineStr">
@@ -36612,7 +36614,7 @@
       </c>
       <c r="S270" s="14" t="inlineStr">
         <is>
-          <t>$77377.67122031367</t>
+          <t>$77377.67122031368</t>
         </is>
       </c>
       <c r="T270" s="14" t="inlineStr">
@@ -36737,7 +36739,7 @@
       </c>
       <c r="P271" s="14" t="inlineStr">
         <is>
-          <t>$410540.6519542148</t>
+          <t>$410540.6519542147</t>
         </is>
       </c>
       <c r="Q271" s="14" t="inlineStr">
@@ -36752,7 +36754,7 @@
       </c>
       <c r="S271" s="14" t="inlineStr">
         <is>
-          <t>$613226.674950846</t>
+          <t>$613226.6749508461</t>
         </is>
       </c>
       <c r="T271" s="14" t="inlineStr">
@@ -36892,7 +36894,7 @@
       </c>
       <c r="S272" s="14" t="inlineStr">
         <is>
-          <t>$147070.84834555053</t>
+          <t>$147070.8483455505</t>
         </is>
       </c>
       <c r="T272" s="14" t="inlineStr">
@@ -37017,7 +37019,7 @@
       </c>
       <c r="P273" s="14" t="inlineStr">
         <is>
-          <t>$358786.54192227684</t>
+          <t>$358786.5419222767</t>
         </is>
       </c>
       <c r="Q273" s="14" t="inlineStr">
@@ -37032,7 +37034,7 @@
       </c>
       <c r="S273" s="14" t="inlineStr">
         <is>
-          <t>$497779.06808453763</t>
+          <t>$497779.06808453775</t>
         </is>
       </c>
       <c r="T273" s="14" t="inlineStr">
@@ -37145,7 +37147,7 @@
         <v>1.270162726687124</v>
       </c>
       <c r="M274" s="14" t="n">
-        <v>1.333833237629746</v>
+        <v>1.333833237629745</v>
       </c>
       <c r="N274" s="14" t="n">
         <v>1.401051026134051</v>
@@ -37285,7 +37287,7 @@
         <v>30.48390544049098</v>
       </c>
       <c r="M275" s="14" t="n">
-        <v>32.0119977031139</v>
+        <v>32.01199770311389</v>
       </c>
       <c r="N275" s="14" t="n">
         <v>33.62522462721723</v>
@@ -37312,7 +37314,7 @@
       </c>
       <c r="S275" s="14" t="inlineStr">
         <is>
-          <t>$372907.7612435738</t>
+          <t>$372907.76124357374</t>
         </is>
       </c>
       <c r="T275" s="14" t="inlineStr">
@@ -37425,7 +37427,7 @@
         <v>44.84252118190425</v>
       </c>
       <c r="M276" s="14" t="n">
-        <v>47.84195521286039</v>
+        <v>47.84195521286038</v>
       </c>
       <c r="N276" s="14" t="n">
         <v>51.05497457905313</v>
@@ -37452,7 +37454,7 @@
       </c>
       <c r="S276" s="14" t="inlineStr">
         <is>
-          <t>$509628.7674511266</t>
+          <t>$509628.76745112654</t>
         </is>
       </c>
       <c r="T276" s="14" t="inlineStr">
@@ -37717,7 +37719,7 @@
       </c>
       <c r="P278" s="14" t="inlineStr">
         <is>
-          <t>$54712.206365406324</t>
+          <t>$54712.20636540632</t>
         </is>
       </c>
       <c r="Q278" s="14" t="inlineStr">
@@ -37732,7 +37734,7 @@
       </c>
       <c r="S278" s="14" t="inlineStr">
         <is>
-          <t>$83424.550672379</t>
+          <t>$83424.55067237902</t>
         </is>
       </c>
       <c r="T278" s="14" t="inlineStr">
@@ -37857,7 +37859,7 @@
       </c>
       <c r="P279" s="14" t="inlineStr">
         <is>
-          <t>$51663.18501533832</t>
+          <t>$51663.185015338306</t>
         </is>
       </c>
       <c r="Q279" s="14" t="inlineStr">
@@ -37872,7 +37874,7 @@
       </c>
       <c r="S279" s="14" t="inlineStr">
         <is>
-          <t>$78775.43755818474</t>
+          <t>$78775.43755818476</t>
         </is>
       </c>
       <c r="T279" s="14" t="inlineStr">
@@ -37997,7 +37999,7 @@
       </c>
       <c r="P280" s="14" t="inlineStr">
         <is>
-          <t>$710706.6515652769</t>
+          <t>$710706.6515652768</t>
         </is>
       </c>
       <c r="Q280" s="14" t="inlineStr">
@@ -38012,7 +38014,7 @@
       </c>
       <c r="S280" s="14" t="inlineStr">
         <is>
-          <t>$930848.9058104854</t>
+          <t>$930848.9058104855</t>
         </is>
       </c>
       <c r="T280" s="14" t="inlineStr">
@@ -38137,7 +38139,7 @@
       </c>
       <c r="P281" s="14" t="inlineStr">
         <is>
-          <t>$73974.6689774684</t>
+          <t>$73974.66897746838</t>
         </is>
       </c>
       <c r="Q281" s="14" t="inlineStr">
@@ -38152,7 +38154,7 @@
       </c>
       <c r="S281" s="14" t="inlineStr">
         <is>
-          <t>$101431.80146439433</t>
+          <t>$101431.80146439436</t>
         </is>
       </c>
       <c r="T281" s="14" t="inlineStr">
@@ -38277,7 +38279,7 @@
       </c>
       <c r="P282" s="14" t="inlineStr">
         <is>
-          <t>$597251.867584664</t>
+          <t>$597251.8675846639</t>
         </is>
       </c>
       <c r="Q282" s="14" t="inlineStr">
@@ -38292,7 +38294,7 @@
       </c>
       <c r="S282" s="14" t="inlineStr">
         <is>
-          <t>$948016.1730674262</t>
+          <t>$948016.1730674264</t>
         </is>
       </c>
       <c r="T282" s="14" t="inlineStr">
@@ -38432,7 +38434,7 @@
       </c>
       <c r="S283" s="14" t="inlineStr">
         <is>
-          <t>$4004.987870326855</t>
+          <t>$4004.9878703268546</t>
         </is>
       </c>
       <c r="T283" s="14" t="inlineStr">
@@ -38557,7 +38559,7 @@
       </c>
       <c r="P284" s="14" t="inlineStr">
         <is>
-          <t>$158156.10967481043</t>
+          <t>$158156.1096748104</t>
         </is>
       </c>
       <c r="Q284" s="14" t="inlineStr">
@@ -38572,7 +38574,7 @@
       </c>
       <c r="S284" s="14" t="inlineStr">
         <is>
-          <t>$170318.06001209564</t>
+          <t>$170318.06001209567</t>
         </is>
       </c>
       <c r="T284" s="14" t="inlineStr">
@@ -38697,7 +38699,7 @@
       </c>
       <c r="P285" s="14" t="inlineStr">
         <is>
-          <t>$37656.216589240576</t>
+          <t>$37656.21658924057</t>
         </is>
       </c>
       <c r="Q285" s="14" t="inlineStr">
@@ -38712,7 +38714,7 @@
       </c>
       <c r="S285" s="14" t="inlineStr">
         <is>
-          <t>$40551.91905049896</t>
+          <t>$40551.91905049897</t>
         </is>
       </c>
       <c r="T285" s="14" t="inlineStr">
@@ -38837,7 +38839,7 @@
       </c>
       <c r="P286" s="14" t="inlineStr">
         <is>
-          <t>$37656.216589240576</t>
+          <t>$37656.21658924057</t>
         </is>
       </c>
       <c r="Q286" s="14" t="inlineStr">
@@ -38852,7 +38854,7 @@
       </c>
       <c r="S286" s="14" t="inlineStr">
         <is>
-          <t>$40551.91905049896</t>
+          <t>$40551.91905049897</t>
         </is>
       </c>
       <c r="T286" s="14" t="inlineStr">
@@ -38977,7 +38979,7 @@
       </c>
       <c r="P287" s="14" t="inlineStr">
         <is>
-          <t>$7531.243317848116</t>
+          <t>$7531.243317848114</t>
         </is>
       </c>
       <c r="Q287" s="14" t="inlineStr">
@@ -38992,7 +38994,7 @@
       </c>
       <c r="S287" s="14" t="inlineStr">
         <is>
-          <t>$8110.383810099792</t>
+          <t>$8110.383810099794</t>
         </is>
       </c>
       <c r="T287" s="14" t="inlineStr">
@@ -39117,7 +39119,7 @@
       </c>
       <c r="P288" s="14" t="inlineStr">
         <is>
-          <t>$405068.43722890905</t>
+          <t>$405068.437228909</t>
         </is>
       </c>
       <c r="Q288" s="14" t="inlineStr">
@@ -39132,7 +39134,7 @@
       </c>
       <c r="S288" s="14" t="inlineStr">
         <is>
-          <t>$537334.4188473133</t>
+          <t>$537334.4188473134</t>
         </is>
       </c>
       <c r="T288" s="14" t="inlineStr">
@@ -39257,7 +39259,7 @@
       </c>
       <c r="P289" s="14" t="inlineStr">
         <is>
-          <t>$102024.65885948371</t>
+          <t>$102024.6588594837</t>
         </is>
       </c>
       <c r="Q289" s="14" t="inlineStr">
@@ -39272,7 +39274,7 @@
       </c>
       <c r="S289" s="14" t="inlineStr">
         <is>
-          <t>$148832.2030379253</t>
+          <t>$148832.20303792533</t>
         </is>
       </c>
       <c r="T289" s="14" t="inlineStr">
@@ -39397,7 +39399,7 @@
       </c>
       <c r="P290" s="14" t="inlineStr">
         <is>
-          <t>$106876.4871523022</t>
+          <t>$106876.48715230217</t>
         </is>
       </c>
       <c r="Q290" s="14" t="inlineStr">
@@ -39412,7 +39414,7 @@
       </c>
       <c r="S290" s="14" t="inlineStr">
         <is>
-          <t>$152875.3701508485</t>
+          <t>$152875.37015084855</t>
         </is>
       </c>
       <c r="T290" s="14" t="inlineStr">
@@ -39537,7 +39539,7 @@
       </c>
       <c r="P291" s="14" t="inlineStr">
         <is>
-          <t>$205028.36310849804</t>
+          <t>$205028.36310849802</t>
         </is>
       </c>
       <c r="Q291" s="14" t="inlineStr">
@@ -39552,7 +39554,7 @@
       </c>
       <c r="S291" s="14" t="inlineStr">
         <is>
-          <t>$293271.1182485665</t>
+          <t>$293271.1182485666</t>
         </is>
       </c>
       <c r="T291" s="14" t="inlineStr">
@@ -39677,7 +39679,7 @@
       </c>
       <c r="P292" s="14" t="inlineStr">
         <is>
-          <t>$235564.50229487018</t>
+          <t>$235564.50229487012</t>
         </is>
       </c>
       <c r="Q292" s="14" t="inlineStr">
@@ -39692,7 +39694,7 @@
       </c>
       <c r="S292" s="14" t="inlineStr">
         <is>
-          <t>$336949.7954345232</t>
+          <t>$336949.7954345233</t>
         </is>
       </c>
       <c r="T292" s="14" t="inlineStr">
@@ -39817,7 +39819,7 @@
       </c>
       <c r="P293" s="14" t="inlineStr">
         <is>
-          <t>$65670.95617558458</t>
+          <t>$65670.95617558456</t>
         </is>
       </c>
       <c r="Q293" s="14" t="inlineStr">
@@ -39832,7 +39834,7 @@
       </c>
       <c r="S293" s="14" t="inlineStr">
         <is>
-          <t>$82624.08877042615</t>
+          <t>$82624.08877042617</t>
         </is>
       </c>
       <c r="T293" s="14" t="inlineStr">
@@ -39957,7 +39959,7 @@
       </c>
       <c r="P294" s="14" t="inlineStr">
         <is>
-          <t>$223619.406313959</t>
+          <t>$223619.40631395899</t>
         </is>
       </c>
       <c r="Q294" s="14" t="inlineStr">
@@ -39972,7 +39974,7 @@
       </c>
       <c r="S294" s="14" t="inlineStr">
         <is>
-          <t>$336242.19036566897</t>
+          <t>$336242.1903656691</t>
         </is>
       </c>
       <c r="T294" s="14" t="inlineStr">
@@ -40085,7 +40087,7 @@
         <v>9.376399454953381</v>
       </c>
       <c r="M295" s="14" t="n">
-        <v>9.176771159399845</v>
+        <v>9.176771159399843</v>
       </c>
       <c r="N295" s="14" t="n">
         <v>8.98367327296882</v>
@@ -40112,7 +40114,7 @@
       </c>
       <c r="S295" s="14" t="inlineStr">
         <is>
-          <t>$39722.93871142454</t>
+          <t>$39722.93871142453</t>
         </is>
       </c>
       <c r="T295" s="14" t="inlineStr">
@@ -40252,7 +40254,7 @@
       </c>
       <c r="S296" s="14" t="inlineStr">
         <is>
-          <t>$39072.389445988534</t>
+          <t>$39072.38944598853</t>
         </is>
       </c>
       <c r="T296" s="14" t="inlineStr">
@@ -40377,7 +40379,7 @@
       </c>
       <c r="P297" s="14" t="inlineStr">
         <is>
-          <t>$4527.739031329582</t>
+          <t>$4527.739031329581</t>
         </is>
       </c>
       <c r="Q297" s="14" t="inlineStr">
@@ -40392,7 +40394,7 @@
       </c>
       <c r="S297" s="14" t="inlineStr">
         <is>
-          <t>$3333.8362441505037</t>
+          <t>$3333.8362441505046</t>
         </is>
       </c>
       <c r="T297" s="14" t="inlineStr">
@@ -40517,7 +40519,7 @@
       </c>
       <c r="P298" s="14" t="inlineStr">
         <is>
-          <t>$4527.880657930849</t>
+          <t>$4527.8806579308475</t>
         </is>
       </c>
       <c r="Q298" s="14" t="inlineStr">
@@ -40532,7 +40534,7 @@
       </c>
       <c r="S298" s="14" t="inlineStr">
         <is>
-          <t>$3334.2029175024522</t>
+          <t>$3334.202917502453</t>
         </is>
       </c>
       <c r="T298" s="14" t="inlineStr">
@@ -40657,7 +40659,7 @@
       </c>
       <c r="P299" s="14" t="inlineStr">
         <is>
-          <t>$151481.68688141185</t>
+          <t>$151481.68688141182</t>
         </is>
       </c>
       <c r="Q299" s="14" t="inlineStr">
@@ -40672,7 +40674,7 @@
       </c>
       <c r="S299" s="14" t="inlineStr">
         <is>
-          <t>$240446.4462670885</t>
+          <t>$240446.44626708856</t>
         </is>
       </c>
       <c r="T299" s="14" t="inlineStr">
@@ -40797,7 +40799,7 @@
       </c>
       <c r="P300" s="14" t="inlineStr">
         <is>
-          <t>$74219.30182224074</t>
+          <t>$74219.30182224073</t>
         </is>
       </c>
       <c r="Q300" s="14" t="inlineStr">
@@ -40812,7 +40814,7 @@
       </c>
       <c r="S300" s="14" t="inlineStr">
         <is>
-          <t>$91877.98759636204</t>
+          <t>$91877.98759636207</t>
         </is>
       </c>
       <c r="T300" s="14" t="inlineStr">
@@ -41345,7 +41347,7 @@
         <v>0.5798344181755594</v>
       </c>
       <c r="M304" s="14" t="n">
-        <v>0.589845392406377</v>
+        <v>0.5898453924063769</v>
       </c>
       <c r="N304" s="14" t="n">
         <v>0.6001815455217978</v>
@@ -41372,7 +41374,7 @@
       </c>
       <c r="S304" s="14" t="inlineStr">
         <is>
-          <t>$3296.395532343282</t>
+          <t>$3296.3955323432815</t>
         </is>
       </c>
       <c r="T304" s="14" t="inlineStr">
@@ -41485,7 +41487,7 @@
         <v>1.670633847456699</v>
       </c>
       <c r="M305" s="14" t="n">
-        <v>1.754379109721671</v>
+        <v>1.75437910972167</v>
       </c>
       <c r="N305" s="14" t="n">
         <v>1.842790074920888</v>
@@ -41512,7 +41514,7 @@
       </c>
       <c r="S305" s="14" t="inlineStr">
         <is>
-          <t>$12787.844768672228</t>
+          <t>$12787.844768672227</t>
         </is>
       </c>
       <c r="T305" s="14" t="inlineStr">
@@ -41625,7 +41627,7 @@
         <v>1.670633847456699</v>
       </c>
       <c r="M306" s="14" t="n">
-        <v>1.754379109721671</v>
+        <v>1.75437910972167</v>
       </c>
       <c r="N306" s="14" t="n">
         <v>1.842790074920888</v>
@@ -41765,7 +41767,7 @@
         <v>3.539890595830071</v>
       </c>
       <c r="M307" s="14" t="n">
-        <v>3.889457720928338</v>
+        <v>3.889457720928337</v>
       </c>
       <c r="N307" s="14" t="n">
         <v>4.113485812729573</v>
@@ -41792,7 +41794,7 @@
       </c>
       <c r="S307" s="14" t="inlineStr">
         <is>
-          <t>$9142.183441620002</t>
+          <t>$9142.18344162</t>
         </is>
       </c>
       <c r="T307" s="14" t="inlineStr">
@@ -41905,7 +41907,7 @@
         <v>8.657302128826771</v>
       </c>
       <c r="M308" s="14" t="n">
-        <v>9.372045860881647</v>
+        <v>9.372045860881645</v>
       </c>
       <c r="N308" s="14" t="n">
         <v>9.872365950550977</v>
@@ -41932,7 +41934,7 @@
       </c>
       <c r="S308" s="14" t="inlineStr">
         <is>
-          <t>$242878.68390622258</t>
+          <t>$242878.68390622255</t>
         </is>
       </c>
       <c r="T308" s="14" t="inlineStr">
@@ -42072,7 +42074,7 @@
       </c>
       <c r="S309" s="14" t="inlineStr">
         <is>
-          <t>$124595.25716963536</t>
+          <t>$124595.25716963534</t>
         </is>
       </c>
       <c r="T309" s="14" t="inlineStr">
@@ -42212,7 +42214,7 @@
       </c>
       <c r="S310" s="14" t="inlineStr">
         <is>
-          <t>$164643.7326884467</t>
+          <t>$164643.73268844667</t>
         </is>
       </c>
       <c r="T310" s="14" t="inlineStr">
@@ -42352,7 +42354,7 @@
       </c>
       <c r="S311" s="14" t="inlineStr">
         <is>
-          <t>$336874.39482873795</t>
+          <t>$336874.3948287379</t>
         </is>
       </c>
       <c r="T311" s="14" t="inlineStr">
@@ -42492,7 +42494,7 @@
       </c>
       <c r="S312" s="14" t="inlineStr">
         <is>
-          <t>$64166.55139595008</t>
+          <t>$64166.551395950075</t>
         </is>
       </c>
       <c r="T312" s="14" t="inlineStr">
@@ -42605,7 +42607,7 @@
         <v>4.348837007673015</v>
       </c>
       <c r="M313" s="14" t="n">
-        <v>5.603760264165507</v>
+        <v>5.603760264165506</v>
       </c>
       <c r="N313" s="14" t="n">
         <v>5.875923457404173</v>
@@ -42632,7 +42634,7 @@
       </c>
       <c r="S313" s="14" t="inlineStr">
         <is>
-          <t>$57444.02317285374</t>
+          <t>$57444.02317285373</t>
         </is>
       </c>
       <c r="T313" s="14" t="inlineStr">
@@ -42772,7 +42774,7 @@
       </c>
       <c r="S314" s="14" t="inlineStr">
         <is>
-          <t>$256666.20558380033</t>
+          <t>$256666.2055838003</t>
         </is>
       </c>
       <c r="T314" s="14" t="inlineStr">
@@ -42885,7 +42887,7 @@
         <v>2.524817618696403</v>
       </c>
       <c r="M315" s="14" t="n">
-        <v>2.574785840651407</v>
+        <v>2.574785840651406</v>
       </c>
       <c r="N315" s="14" t="n">
         <v>2.618954991982792</v>
@@ -42912,7 +42914,7 @@
       </c>
       <c r="S315" s="14" t="inlineStr">
         <is>
-          <t>$31126.090255637646</t>
+          <t>$31126.090255637642</t>
         </is>
       </c>
       <c r="T315" s="14" t="inlineStr">
@@ -43165,7 +43167,7 @@
         <v>0</v>
       </c>
       <c r="M317" s="14" t="n">
-        <v>0.1920497556647229</v>
+        <v>0.1920497556647228</v>
       </c>
       <c r="N317" s="14" t="n">
         <v>0.7519674365765808</v>
@@ -43192,7 +43194,7 @@
       </c>
       <c r="S317" s="14" t="inlineStr">
         <is>
-          <t>$4725.641061478799</t>
+          <t>$4725.641061478798</t>
         </is>
       </c>
       <c r="T317" s="14" t="inlineStr">
@@ -43585,7 +43587,7 @@
         <v>0.7214418440688976</v>
       </c>
       <c r="M320" s="14" t="n">
-        <v>0.7810038217401373</v>
+        <v>0.7810038217401372</v>
       </c>
       <c r="N320" s="14" t="n">
         <v>0.8226971625459146</v>
@@ -43612,7 +43614,7 @@
       </c>
       <c r="S320" s="14" t="inlineStr">
         <is>
-          <t>$16912.568933261067</t>
+          <t>$16912.568933261064</t>
         </is>
       </c>
       <c r="T320" s="14" t="inlineStr">
@@ -44032,7 +44034,7 @@
       </c>
       <c r="S323" s="14" t="inlineStr">
         <is>
-          <t>$159776.6175181587</t>
+          <t>$159776.61751815866</t>
         </is>
       </c>
       <c r="T323" s="14" t="inlineStr">
@@ -44172,7 +44174,7 @@
       </c>
       <c r="S324" s="14" t="inlineStr">
         <is>
-          <t>$246927.49980079065</t>
+          <t>$246927.49980079063</t>
         </is>
       </c>
       <c r="T324" s="14" t="inlineStr">
@@ -44425,7 +44427,7 @@
         <v>5.543479671160879</v>
       </c>
       <c r="M326" s="14" t="n">
-        <v>5.914272863366657</v>
+        <v>5.914272863366656</v>
       </c>
       <c r="N326" s="14" t="n">
         <v>6.311469699541052</v>
@@ -44452,7 +44454,7 @@
       </c>
       <c r="S326" s="14" t="inlineStr">
         <is>
-          <t>$246231.7734256912</t>
+          <t>$246231.77342569118</t>
         </is>
       </c>
       <c r="T326" s="14" t="inlineStr">
@@ -44592,7 +44594,7 @@
       </c>
       <c r="S327" s="14" t="inlineStr">
         <is>
-          <t>$467840.3695088133</t>
+          <t>$467840.36950881325</t>
         </is>
       </c>
       <c r="T327" s="14" t="inlineStr">
@@ -44705,7 +44707,7 @@
         <v>0</v>
       </c>
       <c r="M328" s="14" t="n">
-        <v>5.917773464283971</v>
+        <v>5.91777346428397</v>
       </c>
       <c r="N328" s="14" t="n">
         <v>8.70188122161772</v>
@@ -44732,7 +44734,7 @@
       </c>
       <c r="S328" s="14" t="inlineStr">
         <is>
-          <t>$207596.63386035003</t>
+          <t>$207596.63386035</t>
         </is>
       </c>
       <c r="T328" s="14" t="inlineStr">
@@ -44845,7 +44847,7 @@
         <v>0.9126202509039217</v>
       </c>
       <c r="M329" s="14" t="n">
-        <v>0.8566020754367413</v>
+        <v>0.8566020754367412</v>
       </c>
       <c r="N329" s="14" t="n">
         <v>0.8042265178678712</v>
@@ -44872,7 +44874,7 @@
       </c>
       <c r="S329" s="14" t="inlineStr">
         <is>
-          <t>$132906.06923587507</t>
+          <t>$132906.06923587504</t>
         </is>
       </c>
       <c r="T329" s="14" t="inlineStr">
@@ -44985,7 +44987,7 @@
         <v>0.499960984270787</v>
       </c>
       <c r="M330" s="14" t="n">
-        <v>0.4898727295272353</v>
+        <v>0.4898727295272352</v>
       </c>
       <c r="N330" s="14" t="n">
         <v>0.479564813262481</v>
@@ -45012,7 +45014,7 @@
       </c>
       <c r="S330" s="14" t="inlineStr">
         <is>
-          <t>$9922.482147741337</t>
+          <t>$9922.482147741335</t>
         </is>
       </c>
       <c r="T330" s="14" t="inlineStr">
@@ -45125,7 +45127,7 @@
         <v>0.999921968541574</v>
       </c>
       <c r="M331" s="14" t="n">
-        <v>0.9797454590544705</v>
+        <v>0.9797454590544704</v>
       </c>
       <c r="N331" s="14" t="n">
         <v>0.959129626524962</v>
@@ -45152,7 +45154,7 @@
       </c>
       <c r="S331" s="14" t="inlineStr">
         <is>
-          <t>$19844.964295482674</t>
+          <t>$19844.96429548267</t>
         </is>
       </c>
       <c r="T331" s="14" t="inlineStr">
@@ -45265,7 +45267,7 @@
         <v>0.499960984270787</v>
       </c>
       <c r="M332" s="14" t="n">
-        <v>0.4898727295272353</v>
+        <v>0.4898727295272352</v>
       </c>
       <c r="N332" s="14" t="n">
         <v>0.479564813262481</v>
@@ -45292,7 +45294,7 @@
       </c>
       <c r="S332" s="14" t="inlineStr">
         <is>
-          <t>$9922.482147741337</t>
+          <t>$9922.482147741335</t>
         </is>
       </c>
       <c r="T332" s="14" t="inlineStr">
@@ -45405,7 +45407,7 @@
         <v>0.499960984270787</v>
       </c>
       <c r="M333" s="14" t="n">
-        <v>0.4898727295272353</v>
+        <v>0.4898727295272352</v>
       </c>
       <c r="N333" s="14" t="n">
         <v>0.479564813262481</v>
@@ -45432,7 +45434,7 @@
       </c>
       <c r="S333" s="14" t="inlineStr">
         <is>
-          <t>$9922.482147741337</t>
+          <t>$9922.482147741335</t>
         </is>
       </c>
       <c r="T333" s="14" t="inlineStr">
@@ -45572,7 +45574,7 @@
       </c>
       <c r="S334" s="14" t="inlineStr">
         <is>
-          <t>$109147.30362515467</t>
+          <t>$109147.30362515466</t>
         </is>
       </c>
       <c r="T334" s="14" t="inlineStr">
@@ -45712,7 +45714,7 @@
       </c>
       <c r="S335" s="14" t="inlineStr">
         <is>
-          <t>$46455.593379156424</t>
+          <t>$46455.59337915642</t>
         </is>
       </c>
       <c r="T335" s="14" t="inlineStr">
@@ -45825,7 +45827,7 @@
         <v>0.6164523100188175</v>
       </c>
       <c r="M336" s="14" t="n">
-        <v>0.7618410842261897</v>
+        <v>0.7618410842261896</v>
       </c>
       <c r="N336" s="14" t="n">
         <v>0.8211443309919495</v>
@@ -45852,7 +45854,7 @@
       </c>
       <c r="S336" s="14" t="inlineStr">
         <is>
-          <t>$15485.197793052139</t>
+          <t>$15485.197793052137</t>
         </is>
       </c>
       <c r="T336" s="14" t="inlineStr">
@@ -45965,7 +45967,7 @@
         <v>6.780975410206994</v>
       </c>
       <c r="M337" s="14" t="n">
-        <v>8.380251926488086</v>
+        <v>8.380251926488084</v>
       </c>
       <c r="N337" s="14" t="n">
         <v>9.032587640911444</v>
@@ -45992,7 +45994,7 @@
       </c>
       <c r="S337" s="14" t="inlineStr">
         <is>
-          <t>$170337.17572357354</t>
+          <t>$170337.1757235735</t>
         </is>
       </c>
       <c r="T337" s="14" t="inlineStr">
@@ -46132,7 +46134,7 @@
       </c>
       <c r="S338" s="14" t="inlineStr">
         <is>
-          <t>$370257.76441650215</t>
+          <t>$370257.7644165021</t>
         </is>
       </c>
       <c r="T338" s="14" t="inlineStr">
@@ -46245,7 +46247,7 @@
         <v>9.147190296112408</v>
       </c>
       <c r="M339" s="14" t="n">
-        <v>9.629431586720104</v>
+        <v>9.629431586720102</v>
       </c>
       <c r="N339" s="14" t="n">
         <v>10.1396703478171</v>
@@ -46272,7 +46274,7 @@
       </c>
       <c r="S339" s="14" t="inlineStr">
         <is>
-          <t>$411173.97646918683</t>
+          <t>$411173.9764691868</t>
         </is>
       </c>
       <c r="T339" s="14" t="inlineStr">
@@ -46412,7 +46414,7 @@
       </c>
       <c r="S340" s="14" t="inlineStr">
         <is>
-          <t>$86206.6795469045</t>
+          <t>$86206.67954690449</t>
         </is>
       </c>
       <c r="T340" s="14" t="inlineStr">
@@ -46552,7 +46554,7 @@
       </c>
       <c r="S341" s="14" t="inlineStr">
         <is>
-          <t>$90311.75952532854</t>
+          <t>$90311.75952532853</t>
         </is>
       </c>
       <c r="T341" s="14" t="inlineStr">
@@ -46665,7 +46667,7 @@
         <v>0.5799785764981534</v>
       </c>
       <c r="M342" s="14" t="n">
-        <v>0.6090516484168415</v>
+        <v>0.6090516484168413</v>
       </c>
       <c r="N342" s="14" t="n">
         <v>0.6397444694806137</v>
@@ -46692,7 +46694,7 @@
       </c>
       <c r="S342" s="14" t="inlineStr">
         <is>
-          <t>$8210.167247196281</t>
+          <t>$8210.16724719628</t>
         </is>
       </c>
       <c r="T342" s="14" t="inlineStr">
@@ -46805,7 +46807,7 @@
         <v>2.520736950964445</v>
       </c>
       <c r="M343" s="14" t="n">
-        <v>2.647448741565693</v>
+        <v>2.647448741565692</v>
       </c>
       <c r="N343" s="14" t="n">
         <v>2.780865457063639</v>
@@ -46832,7 +46834,7 @@
       </c>
       <c r="S343" s="14" t="inlineStr">
         <is>
-          <t>$53532.39828625497</t>
+          <t>$53532.39828625496</t>
         </is>
       </c>
       <c r="T343" s="14" t="inlineStr">
@@ -46945,7 +46947,7 @@
         <v>0.5799785764981534</v>
       </c>
       <c r="M344" s="14" t="n">
-        <v>0.6090516484168415</v>
+        <v>0.6090516484168413</v>
       </c>
       <c r="N344" s="14" t="n">
         <v>0.6397444694806137</v>
@@ -46972,7 +46974,7 @@
       </c>
       <c r="S344" s="14" t="inlineStr">
         <is>
-          <t>$12315.25087079442</t>
+          <t>$12315.250870794418</t>
         </is>
       </c>
       <c r="T344" s="14" t="inlineStr">
@@ -47112,7 +47114,7 @@
       </c>
       <c r="S345" s="14" t="inlineStr">
         <is>
-          <t>$47398.156828704654</t>
+          <t>$47398.15682870465</t>
         </is>
       </c>
       <c r="T345" s="14" t="inlineStr">
@@ -47252,7 +47254,7 @@
       </c>
       <c r="S346" s="14" t="inlineStr">
         <is>
-          <t>$189592.62731481862</t>
+          <t>$189592.6273148186</t>
         </is>
       </c>
       <c r="T346" s="14" t="inlineStr">
@@ -47392,7 +47394,7 @@
       </c>
       <c r="S347" s="14" t="inlineStr">
         <is>
-          <t>$5900.190516222524</t>
+          <t>$5900.190516222523</t>
         </is>
       </c>
       <c r="T347" s="14" t="inlineStr">
@@ -47785,7 +47787,7 @@
         <v>0</v>
       </c>
       <c r="M350" s="14" t="n">
-        <v>0.07570615151246879</v>
+        <v>0.07570615151246878</v>
       </c>
       <c r="N350" s="14" t="n">
         <v>4.759837352786082</v>
